--- a/Översikt HEDEMORA.xlsx
+++ b/Översikt HEDEMORA.xlsx
@@ -601,7 +601,7 @@
         <v>45105</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         <v>45996</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>44655</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>46197</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45180</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>46033</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>45239</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>45628</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>45527</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>46033</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>44502</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>45940</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>45527</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>45616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>45919</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>46150</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>45527</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>46078</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>46020</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>45961</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>46178</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>45702</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>45301</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>45527</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>46251</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>45887</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>45469</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>45897</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>46055</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>44489</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>46033</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>46178</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>45702</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>46062</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>44588</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>46033</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>46198</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>46198</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>46239</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>45252</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>46051</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>44502</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>46048</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>45565</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>45664</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>45933</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>44579</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>46051</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>44582</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>44961</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>46239</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>44550</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>44523</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>44883</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>45642</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>45171</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7307,7 +7307,7 @@
         <v>46157</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>46000</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7529,7 +7529,7 @@
         <v>46176</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>46177</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>46178</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>44945</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>46178</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8087,7 +8087,7 @@
         <v>46070</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>46185</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>45670</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>46240</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>45821</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>45825</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
         <v>45001</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>44550</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>45317</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>44880</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>44574</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         <v>44880</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>44864</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
         <v>45889</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>45743</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
         <v>46146</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         <v>46105</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9991,7 +9991,7 @@
         <v>45842</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>44461</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>46164</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>45275</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10429,7 +10429,7 @@
         <v>45610</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         <v>45933</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         <v>46177</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>45008</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10872,7 +10872,7 @@
         <v>45441</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>46062</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>45763</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>44918</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11296,7 +11296,7 @@
         <v>45226</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11410,7 +11410,7 @@
         <v>45615</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11520,7 +11520,7 @@
         <v>44680</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11625,7 +11625,7 @@
         <v>45757</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>46199</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
         <v>46245</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         <v>46204</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12059,7 +12059,7 @@
         <v>46212</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12169,7 +12169,7 @@
         <v>46213</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>46266</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>45818</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12498,7 +12498,7 @@
         <v>45818</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12608,7 +12608,7 @@
         <v>45743</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
         <v>45743</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>45767</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12938,7 +12938,7 @@
         <v>45319</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>45316</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>44550</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13280,7 +13280,7 @@
         <v>46069</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>44523</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         <v>44565</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>44783</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>44462</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>44846</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13770,7 +13770,7 @@
         <v>44466</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13843,7 +13843,7 @@
         <v>44802</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13916,7 +13916,7 @@
         <v>44698</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         <v>44529</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>44588</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14140,7 +14140,7 @@
         <v>44817</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>44491</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14291,7 +14291,7 @@
         <v>44466</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14364,7 +14364,7 @@
         <v>44741</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>44462</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>44720</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         <v>44502</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>44746</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>44859</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>44495</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>44575</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14963,7 +14963,7 @@
         <v>45170</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
         <v>45459</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         <v>45022</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15187,7 +15187,7 @@
         <v>44628</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>44900</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>45175</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>44532</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>45541</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15562,7 +15562,7 @@
         <v>45558</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>45342</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>44956</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>44805</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>45407</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>45070</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16015,7 +16015,7 @@
         <v>45610</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16093,7 +16093,7 @@
         <v>45694</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>45429</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
         <v>45218</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16312,7 +16312,7 @@
         <v>45230</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
         <v>45230</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>45708</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>45099</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>45216</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>44757</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>44501</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>45230</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         <v>45350</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16974,7 +16974,7 @@
         <v>44792</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17047,7 +17047,7 @@
         <v>45527</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
         <v>45845</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>46136</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17281,7 +17281,7 @@
         <v>45484</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>45209</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17432,7 +17432,7 @@
         <v>46056</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
         <v>46069</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17578,7 +17578,7 @@
         <v>46020</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>45889</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>45889</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17807,7 +17807,7 @@
         <v>44750</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>45253</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17958,7 +17958,7 @@
         <v>45895</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18031,7 +18031,7 @@
         <v>45316</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18104,7 +18104,7 @@
         <v>45895</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18182,7 +18182,7 @@
         <v>45534</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18260,7 +18260,7 @@
         <v>45770</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         <v>45770</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>45810</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
         <v>45230</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
         <v>45551</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18630,7 +18630,7 @@
         <v>45906</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>46083</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18781,7 +18781,7 @@
         <v>45287</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18854,7 +18854,7 @@
         <v>46034</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18927,7 +18927,7 @@
         <v>45623</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19000,7 +19000,7 @@
         <v>44914</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19073,7 +19073,7 @@
         <v>45933</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>45566</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19224,7 +19224,7 @@
         <v>45505</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19297,7 +19297,7 @@
         <v>45538</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>45729</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19443,7 +19443,7 @@
         <v>45951</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19516,7 +19516,7 @@
         <v>45951</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>45953</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>45952</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
         <v>45626</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19818,7 +19818,7 @@
         <v>45743</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19891,7 +19891,7 @@
         <v>45729</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>45958</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>45958</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20120,7 +20120,7 @@
         <v>45583</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20193,7 +20193,7 @@
         <v>45576</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         <v>45963</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20339,7 +20339,7 @@
         <v>44783</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20412,7 +20412,7 @@
         <v>45840</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20490,7 +20490,7 @@
         <v>45792</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>45784</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20646,7 +20646,7 @@
         <v>45172</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>44472</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20802,7 +20802,7 @@
         <v>45469</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20875,7 +20875,7 @@
         <v>45933</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20948,7 +20948,7 @@
         <v>45190</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21026,7 +21026,7 @@
         <v>45968</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21099,7 +21099,7 @@
         <v>45840</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21177,7 +21177,7 @@
         <v>45889</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>45971</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>45973</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>44662</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21484,7 +21484,7 @@
         <v>45061</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21562,7 +21562,7 @@
         <v>45975</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
         <v>45702</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21708,7 +21708,7 @@
         <v>45230</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21781,7 +21781,7 @@
         <v>45610</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>46157</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>45756</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>46114</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>44817</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22166,7 +22166,7 @@
         <v>45630</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22239,7 +22239,7 @@
         <v>45880</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>45880</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22395,7 +22395,7 @@
         <v>45278</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>45233</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22541,7 +22541,7 @@
         <v>45268</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22614,7 +22614,7 @@
         <v>45268</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22687,7 +22687,7 @@
         <v>45070</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22760,7 +22760,7 @@
         <v>46161</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
         <v>45763</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>46163</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22979,7 +22979,7 @@
         <v>46164</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23057,7 +23057,7 @@
         <v>46167</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23135,7 +23135,7 @@
         <v>45615</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>46007</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23286,7 +23286,7 @@
         <v>45905</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23364,7 +23364,7 @@
         <v>46169</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>45474</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23520,7 +23520,7 @@
         <v>46169</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23598,7 +23598,7 @@
         <v>45474</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23676,7 +23676,7 @@
         <v>46020</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23749,7 +23749,7 @@
         <v>46021</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23822,7 +23822,7 @@
         <v>45957</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23895,7 +23895,7 @@
         <v>46020</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23968,7 +23968,7 @@
         <v>45940</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24046,7 +24046,7 @@
         <v>45086</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24124,7 +24124,7 @@
         <v>45617</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24202,7 +24202,7 @@
         <v>46030</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24275,7 +24275,7 @@
         <v>45610</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24353,7 +24353,7 @@
         <v>45254</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24426,7 +24426,7 @@
         <v>46035</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>46174</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24577,7 +24577,7 @@
         <v>46033</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24650,7 +24650,7 @@
         <v>46034</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24723,7 +24723,7 @@
         <v>46036</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24801,7 +24801,7 @@
         <v>46174</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24879,7 +24879,7 @@
         <v>45541</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24957,7 +24957,7 @@
         <v>46037</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25030,7 +25030,7 @@
         <v>45980</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25108,7 +25108,7 @@
         <v>45350</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         <v>44546</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25254,7 +25254,7 @@
         <v>46043</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25327,7 +25327,7 @@
         <v>46062</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25400,7 +25400,7 @@
         <v>44462</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25478,7 +25478,7 @@
         <v>46032</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25551,7 +25551,7 @@
         <v>46044</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>46051</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25697,7 +25697,7 @@
         <v>46051</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>46030</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25843,7 +25843,7 @@
         <v>46050</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25916,7 +25916,7 @@
         <v>46051</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25989,7 +25989,7 @@
         <v>45104</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>46177</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26145,7 +26145,7 @@
         <v>46177</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26223,7 +26223,7 @@
         <v>46178</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26301,7 +26301,7 @@
         <v>46136</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26379,7 +26379,7 @@
         <v>46099</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26452,7 +26452,7 @@
         <v>46114</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>46136</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26608,7 +26608,7 @@
         <v>45940</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26686,7 +26686,7 @@
         <v>45920</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26764,7 +26764,7 @@
         <v>44917</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26837,7 +26837,7 @@
         <v>46178</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26915,7 +26915,7 @@
         <v>45252</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26988,7 +26988,7 @@
         <v>46136</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27066,7 +27066,7 @@
         <v>46058</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27139,7 +27139,7 @@
         <v>45260</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27212,7 +27212,7 @@
         <v>46048</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27285,7 +27285,7 @@
         <v>46178</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27363,7 +27363,7 @@
         <v>46033</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27436,7 +27436,7 @@
         <v>45919</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>45943</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>46066</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27665,7 +27665,7 @@
         <v>45267</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27738,7 +27738,7 @@
         <v>46072</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27811,7 +27811,7 @@
         <v>46072</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27884,7 +27884,7 @@
         <v>46072</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27957,7 +27957,7 @@
         <v>44574</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         <v>45509</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28108,7 +28108,7 @@
         <v>45988</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28186,7 +28186,7 @@
         <v>45989</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28264,7 +28264,7 @@
         <v>45995</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28342,7 +28342,7 @@
         <v>45743</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         <v>45296</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28488,7 +28488,7 @@
         <v>46183</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28566,7 +28566,7 @@
         <v>46084</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28639,7 +28639,7 @@
         <v>45163</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>46148</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28795,7 +28795,7 @@
         <v>45239</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28873,7 +28873,7 @@
         <v>46090</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28946,7 +28946,7 @@
         <v>45748</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29019,7 +29019,7 @@
         <v>46185</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29097,7 +29097,7 @@
         <v>46094</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29170,7 +29170,7 @@
         <v>46098</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29248,7 +29248,7 @@
         <v>45615</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         <v>46098</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29404,7 +29404,7 @@
         <v>46098</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29482,7 +29482,7 @@
         <v>46098</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29555,7 +29555,7 @@
         <v>46098</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29628,7 +29628,7 @@
         <v>46099</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29701,7 +29701,7 @@
         <v>45573</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29779,7 +29779,7 @@
         <v>45573</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         <v>46099</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29935,7 +29935,7 @@
         <v>45551</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30013,7 +30013,7 @@
         <v>44575</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30086,7 +30086,7 @@
         <v>45757</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30159,7 +30159,7 @@
         <v>46198</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30237,7 +30237,7 @@
         <v>46105</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30315,7 +30315,7 @@
         <v>46105</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30393,7 +30393,7 @@
         <v>44733</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30466,7 +30466,7 @@
         <v>44911</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30539,7 +30539,7 @@
         <v>45278</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30612,7 +30612,7 @@
         <v>46108</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30685,7 +30685,7 @@
         <v>46111</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30758,7 +30758,7 @@
         <v>46111</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>46199</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30909,7 +30909,7 @@
         <v>44495</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30982,7 +30982,7 @@
         <v>46199</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31060,7 +31060,7 @@
         <v>46119</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31138,7 +31138,7 @@
         <v>46122</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31216,7 +31216,7 @@
         <v>46124</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31294,7 +31294,7 @@
         <v>46125</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31367,7 +31367,7 @@
         <v>46125</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31440,7 +31440,7 @@
         <v>46128</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31518,7 +31518,7 @@
         <v>46128</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31596,7 +31596,7 @@
         <v>46128</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31674,7 +31674,7 @@
         <v>45268</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31747,7 +31747,7 @@
         <v>46129</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31825,7 +31825,7 @@
         <v>46132</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31903,7 +31903,7 @@
         <v>44509</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31976,7 +31976,7 @@
         <v>46134</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32054,7 +32054,7 @@
         <v>46134</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32127,7 +32127,7 @@
         <v>45358</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32200,7 +32200,7 @@
         <v>46139</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32278,7 +32278,7 @@
         <v>45239</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32356,7 +32356,7 @@
         <v>45757</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32429,7 +32429,7 @@
         <v>45541</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>46244</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32580,7 +32580,7 @@
         <v>46212</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32658,7 +32658,7 @@
         <v>46212</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32736,7 +32736,7 @@
         <v>46255</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32814,7 +32814,7 @@
         <v>46255</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32892,7 +32892,7 @@
         <v>46255</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32970,7 +32970,7 @@
         <v>45086</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33048,7 +33048,7 @@
         <v>45701</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33121,7 +33121,7 @@
         <v>44909</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33194,7 +33194,7 @@
         <v>46262</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33267,7 +33267,7 @@
         <v>45194</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33340,7 +33340,7 @@
         <v>45173</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33418,7 +33418,7 @@
         <v>46266</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33496,7 +33496,7 @@
         <v>45055</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33574,7 +33574,7 @@
         <v>46225</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33652,7 +33652,7 @@
         <v>44529</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33725,7 +33725,7 @@
         <v>45113</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33803,7 +33803,7 @@
         <v>46266</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33881,7 +33881,7 @@
         <v>45111</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33959,7 +33959,7 @@
         <v>45278</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34032,7 +34032,7 @@
         <v>46273</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34110,7 +34110,7 @@
         <v>45590</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34183,7 +34183,7 @@
         <v>45187</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34261,7 +34261,7 @@
         <v>45337</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34334,7 +34334,7 @@
         <v>46279</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34412,7 +34412,7 @@
         <v>46279</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34490,7 +34490,7 @@
         <v>46174</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34568,7 +34568,7 @@
         <v>46167</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34646,7 +34646,7 @@
         <v>46279</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34724,7 +34724,7 @@
         <v>45603</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34797,7 +34797,7 @@
         <v>46281</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34875,7 +34875,7 @@
         <v>46281</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34953,7 +34953,7 @@
         <v>46281</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35031,7 +35031,7 @@
         <v>46281</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35109,7 +35109,7 @@
         <v>46281</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35182,7 +35182,7 @@
         <v>46240</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35255,7 +35255,7 @@
         <v>46240</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35328,7 +35328,7 @@
         <v>45462</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35406,7 +35406,7 @@
         <v>46281</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35484,7 +35484,7 @@
         <v>46282</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35557,7 +35557,7 @@
         <v>45799</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35630,7 +35630,7 @@
         <v>46239</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35708,7 +35708,7 @@
         <v>46281</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35786,7 +35786,7 @@
         <v>45429</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35859,7 +35859,7 @@
         <v>45569</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35932,7 +35932,7 @@
         <v>45701</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36005,7 +36005,7 @@
         <v>45818</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>45818</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36161,7 +36161,7 @@
         <v>45827</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36234,7 +36234,7 @@
         <v>45840</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36312,7 +36312,7 @@
         <v>45840</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36390,7 +36390,7 @@
         <v>45848</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36463,7 +36463,7 @@
         <v>45743</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36541,7 +36541,7 @@
         <v>45866</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36614,7 +36614,7 @@
         <v>45866</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36692,7 +36692,7 @@
         <v>45867</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36765,7 +36765,7 @@
         <v>45784</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36843,7 +36843,7 @@
         <v>44102</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36921,7 +36921,7 @@
         <v>45700</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36999,7 +36999,7 @@
         <v>45700</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37077,7 +37077,7 @@
         <v>44585</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37155,7 +37155,7 @@
         <v>44550</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37233,7 +37233,7 @@
         <v>45317</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37311,7 +37311,7 @@
         <v>45316</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37389,7 +37389,7 @@
         <v>44671</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37467,7 +37467,7 @@
         <v>45720</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37545,7 +37545,7 @@
         <v>45706</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37623,7 +37623,7 @@
         <v>45906</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37701,7 +37701,7 @@
         <v>45989</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37779,7 +37779,7 @@
         <v>45995</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37857,7 +37857,7 @@
         <v>46070</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37935,7 +37935,7 @@
         <v>45700</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38013,7 +38013,7 @@
         <v>46142</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38091,7 +38091,7 @@
         <v>46125</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38169,7 +38169,7 @@
         <v>45971</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38242,7 +38242,7 @@
         <v>46085</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>

--- a/Översikt HEDEMORA.xlsx
+++ b/Översikt HEDEMORA.xlsx
@@ -601,7 +601,7 @@
         <v>45105</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         <v>45996</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>44655</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>46197</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45180</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>46033</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>45628</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>45239</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>45527</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>46033</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>44502</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>45940</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>45527</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>45616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>45919</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>46150</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>45527</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>46078</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>46020</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>45961</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>46178</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>45702</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>45527</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>46251</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>45301</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>45887</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>45469</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>45897</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>44489</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>46033</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>46055</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>46178</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>45702</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>46062</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>44588</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>46033</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>46198</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>46198</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>46239</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>44502</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>46048</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>46051</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>45252</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>44579</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>46051</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>45664</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         <v>44582</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>45933</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>44961</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>45565</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>46239</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>44550</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>44523</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>44883</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>44945</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>46070</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>46000</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>46157</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>46177</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         <v>46176</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>46178</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>46178</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         <v>45821</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>46185</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         <v>45670</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>45825</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>45642</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         <v>46240</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>45171</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
         <v>45001</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>44550</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>45317</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>44880</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>44574</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         <v>44880</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>44864</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
         <v>45889</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>44918</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>45275</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         <v>46062</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>45441</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>45008</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>45743</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         <v>45842</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>45226</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>45818</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>45610</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>45818</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         <v>46105</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>46146</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>45757</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>46164</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11301,7 +11301,7 @@
         <v>45743</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>45743</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>45767</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>46177</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
         <v>45933</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>46204</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         <v>46212</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>46213</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>44680</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>46266</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12394,7 +12394,7 @@
         <v>45763</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
         <v>45615</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12609,7 +12609,7 @@
         <v>46245</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         <v>46199</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>44550</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
         <v>45319</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         <v>45316</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13171,7 +13171,7 @@
         <v>46069</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13281,7 +13281,7 @@
         <v>44523</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13359,7 +13359,7 @@
         <v>44565</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13432,7 +13432,7 @@
         <v>44783</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>44846</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>44466</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>44802</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13729,7 +13729,7 @@
         <v>44698</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13802,7 +13802,7 @@
         <v>44529</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         <v>44588</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13953,7 +13953,7 @@
         <v>44817</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>44491</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>44466</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         <v>44741</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>44720</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         <v>44502</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>44746</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>44859</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>44495</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>44575</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>45626</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14776,7 +14776,7 @@
         <v>45743</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14849,7 +14849,7 @@
         <v>45527</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         <v>45541</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15005,7 +15005,7 @@
         <v>44817</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>45239</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>46020</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15234,7 +15234,7 @@
         <v>46020</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>45505</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15380,7 +15380,7 @@
         <v>45459</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
         <v>45940</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>46021</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>46030</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15677,7 +15677,7 @@
         <v>45509</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>45462</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>44914</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>46033</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>45845</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>46034</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16125,7 +16125,7 @@
         <v>46035</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16198,7 +16198,7 @@
         <v>45534</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>46036</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>46037</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16427,7 +16427,7 @@
         <v>45889</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>45889</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         <v>45770</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>45770</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16729,7 +16729,7 @@
         <v>45895</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>45980</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>46044</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16958,7 +16958,7 @@
         <v>44917</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17031,7 +17031,7 @@
         <v>46043</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
         <v>46032</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>46050</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17250,7 +17250,7 @@
         <v>45538</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>45799</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>46051</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         <v>45906</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>46051</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17620,7 +17620,7 @@
         <v>46051</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17693,7 +17693,7 @@
         <v>45541</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>45252</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17844,7 +17844,7 @@
         <v>45260</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17917,7 +17917,7 @@
         <v>45429</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17990,7 +17990,7 @@
         <v>46048</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18063,7 +18063,7 @@
         <v>46066</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>45055</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18219,7 +18219,7 @@
         <v>46072</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18292,7 +18292,7 @@
         <v>46072</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18365,7 +18365,7 @@
         <v>46072</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18438,7 +18438,7 @@
         <v>45022</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>45541</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>44956</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18672,7 +18672,7 @@
         <v>45988</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>45989</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>45995</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18906,7 +18906,7 @@
         <v>45573</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18984,7 +18984,7 @@
         <v>45573</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>45701</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>45569</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>46084</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19281,7 +19281,7 @@
         <v>45933</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19354,7 +19354,7 @@
         <v>46090</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>45230</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>46094</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>45576</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>46099</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19719,7 +19719,7 @@
         <v>46098</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19797,7 +19797,7 @@
         <v>46098</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19870,7 +19870,7 @@
         <v>46098</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>46098</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>46098</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         <v>46099</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>46105</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20255,7 +20255,7 @@
         <v>46105</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20333,7 +20333,7 @@
         <v>45951</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>45951</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20479,7 +20479,7 @@
         <v>45953</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20557,7 +20557,7 @@
         <v>45952</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20630,7 +20630,7 @@
         <v>46108</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20703,7 +20703,7 @@
         <v>46111</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>46111</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20849,7 +20849,7 @@
         <v>45958</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>45958</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>45254</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>46119</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>45963</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>46125</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21302,7 +21302,7 @@
         <v>45792</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21380,7 +21380,7 @@
         <v>45784</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21458,7 +21458,7 @@
         <v>46124</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>44783</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21609,7 +21609,7 @@
         <v>45840</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21687,7 +21687,7 @@
         <v>46122</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21765,7 +21765,7 @@
         <v>46125</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21838,7 +21838,7 @@
         <v>45968</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21911,7 +21911,7 @@
         <v>45933</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21984,7 +21984,7 @@
         <v>45889</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>44509</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22135,7 +22135,7 @@
         <v>45233</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>45840</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22286,7 +22286,7 @@
         <v>45971</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22359,7 +22359,7 @@
         <v>45973</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22437,7 +22437,7 @@
         <v>45818</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22515,7 +22515,7 @@
         <v>46128</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22593,7 +22593,7 @@
         <v>45818</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>46128</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22749,7 +22749,7 @@
         <v>45975</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22822,7 +22822,7 @@
         <v>46134</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22900,7 +22900,7 @@
         <v>46132</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22978,7 +22978,7 @@
         <v>46134</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23051,7 +23051,7 @@
         <v>45061</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>45268</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>45880</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23280,7 +23280,7 @@
         <v>44805</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23358,7 +23358,7 @@
         <v>45880</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23436,7 +23436,7 @@
         <v>46136</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23514,7 +23514,7 @@
         <v>46083</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23587,7 +23587,7 @@
         <v>46056</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23660,7 +23660,7 @@
         <v>44750</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23738,7 +23738,7 @@
         <v>45708</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23811,7 +23811,7 @@
         <v>45895</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23884,7 +23884,7 @@
         <v>45905</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23962,7 +23962,7 @@
         <v>45484</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>45748</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24113,7 +24113,7 @@
         <v>46007</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24186,7 +24186,7 @@
         <v>45810</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>45209</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24332,7 +24332,7 @@
         <v>45551</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>46069</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24483,7 +24483,7 @@
         <v>46034</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24556,7 +24556,7 @@
         <v>45729</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24629,7 +24629,7 @@
         <v>46139</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24707,7 +24707,7 @@
         <v>45216</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24780,7 +24780,7 @@
         <v>46020</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24853,7 +24853,7 @@
         <v>45070</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24926,7 +24926,7 @@
         <v>45230</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24999,7 +24999,7 @@
         <v>45827</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25072,7 +25072,7 @@
         <v>45474</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>44529</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25223,7 +25223,7 @@
         <v>45757</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25296,7 +25296,7 @@
         <v>45099</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>44900</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25442,7 +25442,7 @@
         <v>46114</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25520,7 +25520,7 @@
         <v>45469</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25593,7 +25593,7 @@
         <v>45104</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25671,7 +25671,7 @@
         <v>45278</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25744,7 +25744,7 @@
         <v>45630</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>46157</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25895,7 +25895,7 @@
         <v>45702</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>45840</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26046,7 +26046,7 @@
         <v>45566</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>45840</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26202,7 +26202,7 @@
         <v>45350</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26275,7 +26275,7 @@
         <v>44501</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26348,7 +26348,7 @@
         <v>46164</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26426,7 +26426,7 @@
         <v>46161</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26499,7 +26499,7 @@
         <v>46163</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26572,7 +26572,7 @@
         <v>45848</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26645,7 +26645,7 @@
         <v>45358</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26718,7 +26718,7 @@
         <v>46167</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26796,7 +26796,7 @@
         <v>45743</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26874,7 +26874,7 @@
         <v>44546</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26947,7 +26947,7 @@
         <v>46169</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27025,7 +27025,7 @@
         <v>45957</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>46169</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27176,7 +27176,7 @@
         <v>45239</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27254,7 +27254,7 @@
         <v>45218</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
         <v>45287</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27400,7 +27400,7 @@
         <v>44628</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27478,7 +27478,7 @@
         <v>46062</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27551,7 +27551,7 @@
         <v>45163</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27629,7 +27629,7 @@
         <v>45866</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27707,7 +27707,7 @@
         <v>45866</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27780,7 +27780,7 @@
         <v>46030</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27853,7 +27853,7 @@
         <v>46174</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27931,7 +27931,7 @@
         <v>46174</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>45867</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>46177</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28160,7 +28160,7 @@
         <v>46177</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28238,7 +28238,7 @@
         <v>46099</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28311,7 +28311,7 @@
         <v>46178</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28389,7 +28389,7 @@
         <v>45474</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28467,7 +28467,7 @@
         <v>46114</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28545,7 +28545,7 @@
         <v>45943</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28618,7 +28618,7 @@
         <v>45919</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28696,7 +28696,7 @@
         <v>46178</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>45920</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28852,7 +28852,7 @@
         <v>45940</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28930,7 +28930,7 @@
         <v>46033</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29003,7 +29003,7 @@
         <v>46136</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>45407</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29159,7 +29159,7 @@
         <v>46136</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29237,7 +29237,7 @@
         <v>46136</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29315,7 +29315,7 @@
         <v>45429</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29388,7 +29388,7 @@
         <v>46183</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>45170</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29539,7 +29539,7 @@
         <v>45617</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29617,7 +29617,7 @@
         <v>44532</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29690,7 +29690,7 @@
         <v>46185</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29768,7 +29768,7 @@
         <v>45278</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>46148</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>45342</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29992,7 +29992,7 @@
         <v>46198</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30070,7 +30070,7 @@
         <v>45551</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>45784</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>44662</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30304,7 +30304,7 @@
         <v>45350</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30377,7 +30377,7 @@
         <v>45610</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30455,7 +30455,7 @@
         <v>45729</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30528,7 +30528,7 @@
         <v>46255</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30606,7 +30606,7 @@
         <v>46255</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30684,7 +30684,7 @@
         <v>46255</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30762,7 +30762,7 @@
         <v>45086</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30840,7 +30840,7 @@
         <v>46212</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30918,7 +30918,7 @@
         <v>46212</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30996,7 +30996,7 @@
         <v>45701</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31069,7 +31069,7 @@
         <v>45175</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31142,7 +31142,7 @@
         <v>45756</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31215,7 +31215,7 @@
         <v>45253</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31288,7 +31288,7 @@
         <v>46262</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31361,7 +31361,7 @@
         <v>45194</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31434,7 +31434,7 @@
         <v>44792</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31507,7 +31507,7 @@
         <v>45316</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31580,7 +31580,7 @@
         <v>45268</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31653,7 +31653,7 @@
         <v>46266</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31731,7 +31731,7 @@
         <v>46266</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31809,7 +31809,7 @@
         <v>46225</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31887,7 +31887,7 @@
         <v>45757</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31960,7 +31960,7 @@
         <v>45267</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32033,7 +32033,7 @@
         <v>46273</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32111,7 +32111,7 @@
         <v>44495</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32184,7 +32184,7 @@
         <v>45268</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>46167</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32335,7 +32335,7 @@
         <v>45615</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32413,7 +32413,7 @@
         <v>45296</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32486,7 +32486,7 @@
         <v>46279</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32564,7 +32564,7 @@
         <v>46279</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32642,7 +32642,7 @@
         <v>46174</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32720,7 +32720,7 @@
         <v>46279</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32798,7 +32798,7 @@
         <v>46281</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32871,7 +32871,7 @@
         <v>46282</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32944,7 +32944,7 @@
         <v>46281</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33022,7 +33022,7 @@
         <v>46281</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33100,7 +33100,7 @@
         <v>45173</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33178,7 +33178,7 @@
         <v>46239</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33256,7 +33256,7 @@
         <v>46281</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33334,7 +33334,7 @@
         <v>46281</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>46240</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33485,7 +33485,7 @@
         <v>44574</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33563,7 +33563,7 @@
         <v>46240</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33636,7 +33636,7 @@
         <v>46281</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33714,7 +33714,7 @@
         <v>46286</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33787,7 +33787,7 @@
         <v>46281</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33865,7 +33865,7 @@
         <v>44575</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33938,7 +33938,7 @@
         <v>46058</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34011,7 +34011,7 @@
         <v>44911</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>44757</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34162,7 +34162,7 @@
         <v>44472</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34240,7 +34240,7 @@
         <v>46244</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34313,7 +34313,7 @@
         <v>45086</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34391,7 +34391,7 @@
         <v>46199</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34469,7 +34469,7 @@
         <v>46178</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34547,7 +34547,7 @@
         <v>45172</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34625,7 +34625,7 @@
         <v>45113</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34703,7 +34703,7 @@
         <v>44909</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34776,7 +34776,7 @@
         <v>45230</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34849,7 +34849,7 @@
         <v>45190</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34927,7 +34927,7 @@
         <v>45694</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35000,7 +35000,7 @@
         <v>44733</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35073,7 +35073,7 @@
         <v>45230</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35146,7 +35146,7 @@
         <v>45583</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35219,7 +35219,7 @@
         <v>45610</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35297,7 +35297,7 @@
         <v>45070</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35370,7 +35370,7 @@
         <v>45558</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35443,7 +35443,7 @@
         <v>45230</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35516,7 +35516,7 @@
         <v>45623</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35589,7 +35589,7 @@
         <v>45610</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35667,7 +35667,7 @@
         <v>45615</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35745,7 +35745,7 @@
         <v>45743</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35818,7 +35818,7 @@
         <v>45278</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35891,7 +35891,7 @@
         <v>45187</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>45337</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36042,7 +36042,7 @@
         <v>45111</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36120,7 +36120,7 @@
         <v>45590</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36193,7 +36193,7 @@
         <v>45603</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36266,7 +36266,7 @@
         <v>44102</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36344,7 +36344,7 @@
         <v>44585</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36422,7 +36422,7 @@
         <v>44550</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36500,7 +36500,7 @@
         <v>44671</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36578,7 +36578,7 @@
         <v>45700</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36656,7 +36656,7 @@
         <v>45700</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36734,7 +36734,7 @@
         <v>45317</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36812,7 +36812,7 @@
         <v>45316</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36890,7 +36890,7 @@
         <v>45720</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36968,7 +36968,7 @@
         <v>45706</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37046,7 +37046,7 @@
         <v>45906</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37124,7 +37124,7 @@
         <v>45989</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37202,7 +37202,7 @@
         <v>45995</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>46070</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37358,7 +37358,7 @@
         <v>45700</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37436,7 +37436,7 @@
         <v>46142</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37514,7 +37514,7 @@
         <v>46125</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37592,7 +37592,7 @@
         <v>45971</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37665,7 +37665,7 @@
         <v>46085</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>

--- a/Översikt HEDEMORA.xlsx
+++ b/Översikt HEDEMORA.xlsx
@@ -601,7 +601,7 @@
         <v>45105</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         <v>45996</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>44655</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>46197</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45180</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>46033</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>45628</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>45239</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>45527</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>46033</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>44502</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>45940</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>45527</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>45616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>45919</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>46150</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>45527</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>46078</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>46020</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>45961</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>46178</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>45702</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>45527</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>46251</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>45301</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>45887</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>45469</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>45897</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>44489</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>46033</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>46055</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>46178</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>45702</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>46062</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>44588</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>46033</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>46198</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>46198</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>46239</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>44502</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>46048</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>46051</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>45252</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>44579</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>46051</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>45664</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         <v>44582</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>45933</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>44961</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>45565</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>46239</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>44550</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>44523</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>44883</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>44945</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>46070</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>46000</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>46157</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>46177</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         <v>46176</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>46178</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>46178</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         <v>45821</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>46185</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         <v>45670</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>45825</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>45642</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         <v>46240</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>45171</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
         <v>45001</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>44550</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>45317</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>44880</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>44574</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         <v>44880</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>44864</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
         <v>45889</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>44918</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>45275</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         <v>46062</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>45441</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>45008</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>45743</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         <v>45842</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>45226</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>45818</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>45610</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>45818</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         <v>46105</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>46146</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>45757</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>46164</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11301,7 +11301,7 @@
         <v>45743</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>45743</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>45767</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>46177</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
         <v>45933</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>46204</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         <v>46212</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>46213</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>44680</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>46266</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12394,7 +12394,7 @@
         <v>45763</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
         <v>45615</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12609,7 +12609,7 @@
         <v>46245</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         <v>46199</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>44550</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
         <v>45319</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         <v>45316</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13171,7 +13171,7 @@
         <v>46069</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13281,7 +13281,7 @@
         <v>44523</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13359,7 +13359,7 @@
         <v>44565</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13432,7 +13432,7 @@
         <v>44783</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>44846</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>44466</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>44802</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13729,7 +13729,7 @@
         <v>44698</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13802,7 +13802,7 @@
         <v>44529</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         <v>44588</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13953,7 +13953,7 @@
         <v>44817</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>44491</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>44466</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         <v>44741</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>44720</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         <v>44502</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>44746</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>44859</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>44495</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>44575</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>45626</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14776,7 +14776,7 @@
         <v>45743</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14849,7 +14849,7 @@
         <v>45527</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         <v>45541</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15005,7 +15005,7 @@
         <v>44817</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>45239</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>46020</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15234,7 +15234,7 @@
         <v>46020</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>45505</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15380,7 +15380,7 @@
         <v>45459</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
         <v>45940</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>46021</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>46030</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15677,7 +15677,7 @@
         <v>45509</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>45462</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>44914</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>46033</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>45845</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>46034</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16125,7 +16125,7 @@
         <v>46035</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16198,7 +16198,7 @@
         <v>45534</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>46036</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>46037</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16427,7 +16427,7 @@
         <v>45889</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>45889</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         <v>45770</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>45770</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16729,7 +16729,7 @@
         <v>45895</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>45980</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>46044</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16958,7 +16958,7 @@
         <v>44917</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17031,7 +17031,7 @@
         <v>46043</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
         <v>46032</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>46050</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17250,7 +17250,7 @@
         <v>45538</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>45799</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>46051</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         <v>45906</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>46051</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17620,7 +17620,7 @@
         <v>46051</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17693,7 +17693,7 @@
         <v>45541</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>45252</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17844,7 +17844,7 @@
         <v>45260</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17917,7 +17917,7 @@
         <v>45429</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17990,7 +17990,7 @@
         <v>46048</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18063,7 +18063,7 @@
         <v>46066</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>45055</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18219,7 +18219,7 @@
         <v>46072</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18292,7 +18292,7 @@
         <v>46072</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18365,7 +18365,7 @@
         <v>46072</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18438,7 +18438,7 @@
         <v>45022</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>45541</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>44956</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18672,7 +18672,7 @@
         <v>45988</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>45989</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>45995</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18906,7 +18906,7 @@
         <v>45573</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18984,7 +18984,7 @@
         <v>45573</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>45701</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>45569</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>46084</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19281,7 +19281,7 @@
         <v>45933</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19354,7 +19354,7 @@
         <v>46090</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>45230</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>46094</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>45576</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>46099</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19719,7 +19719,7 @@
         <v>46098</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19797,7 +19797,7 @@
         <v>46098</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19870,7 +19870,7 @@
         <v>46098</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>46098</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>46098</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         <v>46099</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>46105</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20255,7 +20255,7 @@
         <v>46105</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20333,7 +20333,7 @@
         <v>45951</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>45951</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20479,7 +20479,7 @@
         <v>45953</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20557,7 +20557,7 @@
         <v>45952</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20630,7 +20630,7 @@
         <v>46108</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20703,7 +20703,7 @@
         <v>46111</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>46111</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20849,7 +20849,7 @@
         <v>45958</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>45958</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>45254</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>46119</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>45963</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>46125</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21302,7 +21302,7 @@
         <v>45792</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21380,7 +21380,7 @@
         <v>45784</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21458,7 +21458,7 @@
         <v>46124</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>44783</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21609,7 +21609,7 @@
         <v>45840</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21687,7 +21687,7 @@
         <v>46122</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21765,7 +21765,7 @@
         <v>46125</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21838,7 +21838,7 @@
         <v>45968</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21911,7 +21911,7 @@
         <v>45933</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21984,7 +21984,7 @@
         <v>45889</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>44509</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22135,7 +22135,7 @@
         <v>45233</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>45840</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22286,7 +22286,7 @@
         <v>45971</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22359,7 +22359,7 @@
         <v>45973</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22437,7 +22437,7 @@
         <v>45818</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22515,7 +22515,7 @@
         <v>46128</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22593,7 +22593,7 @@
         <v>45818</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>46128</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22749,7 +22749,7 @@
         <v>45975</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22822,7 +22822,7 @@
         <v>46134</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22900,7 +22900,7 @@
         <v>46132</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22978,7 +22978,7 @@
         <v>46134</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23051,7 +23051,7 @@
         <v>45061</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>45268</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>45880</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23280,7 +23280,7 @@
         <v>44805</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23358,7 +23358,7 @@
         <v>45880</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23436,7 +23436,7 @@
         <v>46136</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23514,7 +23514,7 @@
         <v>46083</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23587,7 +23587,7 @@
         <v>46056</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23660,7 +23660,7 @@
         <v>44750</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23738,7 +23738,7 @@
         <v>45708</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23811,7 +23811,7 @@
         <v>45895</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23884,7 +23884,7 @@
         <v>45905</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23962,7 +23962,7 @@
         <v>45484</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>45748</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24113,7 +24113,7 @@
         <v>46007</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24186,7 +24186,7 @@
         <v>45810</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>45209</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24332,7 +24332,7 @@
         <v>45551</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>46069</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24483,7 +24483,7 @@
         <v>46034</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24556,7 +24556,7 @@
         <v>45729</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24629,7 +24629,7 @@
         <v>46139</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24707,7 +24707,7 @@
         <v>45216</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24780,7 +24780,7 @@
         <v>46020</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24853,7 +24853,7 @@
         <v>45070</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24926,7 +24926,7 @@
         <v>45230</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24999,7 +24999,7 @@
         <v>45827</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25072,7 +25072,7 @@
         <v>45474</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>44529</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25223,7 +25223,7 @@
         <v>45757</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25296,7 +25296,7 @@
         <v>45099</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>44900</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25442,7 +25442,7 @@
         <v>46114</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25520,7 +25520,7 @@
         <v>45469</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25593,7 +25593,7 @@
         <v>45104</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25671,7 +25671,7 @@
         <v>45278</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25744,7 +25744,7 @@
         <v>45630</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>46157</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25895,7 +25895,7 @@
         <v>45702</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>45840</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26046,7 +26046,7 @@
         <v>45566</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>45840</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26202,7 +26202,7 @@
         <v>45350</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26275,7 +26275,7 @@
         <v>44501</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26348,7 +26348,7 @@
         <v>46164</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26426,7 +26426,7 @@
         <v>46161</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26499,7 +26499,7 @@
         <v>46163</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26572,7 +26572,7 @@
         <v>45848</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26645,7 +26645,7 @@
         <v>45358</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26718,7 +26718,7 @@
         <v>46167</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26796,7 +26796,7 @@
         <v>45743</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26874,7 +26874,7 @@
         <v>44546</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26947,7 +26947,7 @@
         <v>46169</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27025,7 +27025,7 @@
         <v>45957</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>46169</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27176,7 +27176,7 @@
         <v>45239</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27254,7 +27254,7 @@
         <v>45218</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
         <v>45287</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27400,7 +27400,7 @@
         <v>44628</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27478,7 +27478,7 @@
         <v>46062</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27551,7 +27551,7 @@
         <v>45163</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27629,7 +27629,7 @@
         <v>45866</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27707,7 +27707,7 @@
         <v>45866</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27780,7 +27780,7 @@
         <v>46030</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27853,7 +27853,7 @@
         <v>46174</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27931,7 +27931,7 @@
         <v>46174</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>45867</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>46177</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28160,7 +28160,7 @@
         <v>46177</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28238,7 +28238,7 @@
         <v>46099</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28311,7 +28311,7 @@
         <v>46178</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28389,7 +28389,7 @@
         <v>45474</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28467,7 +28467,7 @@
         <v>46114</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28545,7 +28545,7 @@
         <v>45943</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28618,7 +28618,7 @@
         <v>45919</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28696,7 +28696,7 @@
         <v>46178</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>45920</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28852,7 +28852,7 @@
         <v>45940</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28930,7 +28930,7 @@
         <v>46033</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29003,7 +29003,7 @@
         <v>46136</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>45407</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29159,7 +29159,7 @@
         <v>46136</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29237,7 +29237,7 @@
         <v>46136</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29315,7 +29315,7 @@
         <v>45429</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29388,7 +29388,7 @@
         <v>46183</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>45170</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29539,7 +29539,7 @@
         <v>45617</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29617,7 +29617,7 @@
         <v>44532</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29690,7 +29690,7 @@
         <v>46185</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29768,7 +29768,7 @@
         <v>45278</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>46148</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>45342</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29992,7 +29992,7 @@
         <v>46198</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30070,7 +30070,7 @@
         <v>45551</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>45784</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>44662</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30304,7 +30304,7 @@
         <v>45350</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30377,7 +30377,7 @@
         <v>45610</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30455,7 +30455,7 @@
         <v>45729</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30528,7 +30528,7 @@
         <v>46255</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30606,7 +30606,7 @@
         <v>46255</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30684,7 +30684,7 @@
         <v>46255</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30762,7 +30762,7 @@
         <v>45086</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30840,7 +30840,7 @@
         <v>46212</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30918,7 +30918,7 @@
         <v>46212</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30996,7 +30996,7 @@
         <v>45701</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31069,7 +31069,7 @@
         <v>45175</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31142,7 +31142,7 @@
         <v>45756</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31215,7 +31215,7 @@
         <v>45253</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31288,7 +31288,7 @@
         <v>46262</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31361,7 +31361,7 @@
         <v>45194</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31434,7 +31434,7 @@
         <v>44792</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31507,7 +31507,7 @@
         <v>45316</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31580,7 +31580,7 @@
         <v>45268</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31653,7 +31653,7 @@
         <v>46266</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31731,7 +31731,7 @@
         <v>46266</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31809,7 +31809,7 @@
         <v>46225</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31887,7 +31887,7 @@
         <v>45757</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31960,7 +31960,7 @@
         <v>45267</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32033,7 +32033,7 @@
         <v>46273</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32111,7 +32111,7 @@
         <v>44495</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32184,7 +32184,7 @@
         <v>45268</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>46167</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32335,7 +32335,7 @@
         <v>45615</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32413,7 +32413,7 @@
         <v>45296</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32486,7 +32486,7 @@
         <v>46279</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32564,7 +32564,7 @@
         <v>46279</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32642,7 +32642,7 @@
         <v>46174</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32720,7 +32720,7 @@
         <v>46279</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32798,7 +32798,7 @@
         <v>46281</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32871,7 +32871,7 @@
         <v>46282</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32944,7 +32944,7 @@
         <v>46281</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33022,7 +33022,7 @@
         <v>46281</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33100,7 +33100,7 @@
         <v>45173</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33178,7 +33178,7 @@
         <v>46239</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33256,7 +33256,7 @@
         <v>46281</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33334,7 +33334,7 @@
         <v>46281</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>46240</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33485,7 +33485,7 @@
         <v>44574</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33563,7 +33563,7 @@
         <v>46240</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33636,7 +33636,7 @@
         <v>46281</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33714,7 +33714,7 @@
         <v>46286</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33787,7 +33787,7 @@
         <v>46281</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33865,7 +33865,7 @@
         <v>44575</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33938,7 +33938,7 @@
         <v>46058</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34011,7 +34011,7 @@
         <v>44911</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>44757</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34162,7 +34162,7 @@
         <v>44472</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34240,7 +34240,7 @@
         <v>46244</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34313,7 +34313,7 @@
         <v>45086</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34391,7 +34391,7 @@
         <v>46199</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34469,7 +34469,7 @@
         <v>46178</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34547,7 +34547,7 @@
         <v>45172</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34625,7 +34625,7 @@
         <v>45113</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34703,7 +34703,7 @@
         <v>44909</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34776,7 +34776,7 @@
         <v>45230</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34849,7 +34849,7 @@
         <v>45190</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34927,7 +34927,7 @@
         <v>45694</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35000,7 +35000,7 @@
         <v>44733</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35073,7 +35073,7 @@
         <v>45230</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35146,7 +35146,7 @@
         <v>45583</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35219,7 +35219,7 @@
         <v>45610</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35297,7 +35297,7 @@
         <v>45070</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35370,7 +35370,7 @@
         <v>45558</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35443,7 +35443,7 @@
         <v>45230</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35516,7 +35516,7 @@
         <v>45623</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35589,7 +35589,7 @@
         <v>45610</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35667,7 +35667,7 @@
         <v>45615</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35745,7 +35745,7 @@
         <v>45743</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35818,7 +35818,7 @@
         <v>45278</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35891,7 +35891,7 @@
         <v>45187</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>45337</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36042,7 +36042,7 @@
         <v>45111</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36120,7 +36120,7 @@
         <v>45590</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36193,7 +36193,7 @@
         <v>45603</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36266,7 +36266,7 @@
         <v>44102</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36344,7 +36344,7 @@
         <v>44585</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36422,7 +36422,7 @@
         <v>44550</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36500,7 +36500,7 @@
         <v>44671</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36578,7 +36578,7 @@
         <v>45700</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36656,7 +36656,7 @@
         <v>45700</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36734,7 +36734,7 @@
         <v>45317</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36812,7 +36812,7 @@
         <v>45316</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36890,7 +36890,7 @@
         <v>45720</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36968,7 +36968,7 @@
         <v>45706</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37046,7 +37046,7 @@
         <v>45906</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37124,7 +37124,7 @@
         <v>45989</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37202,7 +37202,7 @@
         <v>45995</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>46070</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37358,7 +37358,7 @@
         <v>45700</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37436,7 +37436,7 @@
         <v>46142</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37514,7 +37514,7 @@
         <v>46125</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37592,7 +37592,7 @@
         <v>45971</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37665,7 +37665,7 @@
         <v>46085</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>

--- a/Översikt HEDEMORA.xlsx
+++ b/Översikt HEDEMORA.xlsx
@@ -601,7 +601,7 @@
         <v>45105</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -644,13 +644,13 @@
         <v>12</v>
       </c>
       <c r="S2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="T2" t="n">
-        <v>857</v>
+        <v>878</v>
       </c>
       <c r="U2" t="n">
-        <v>857</v>
+        <v>878</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -696,6 +696,7 @@
 Vedticka
 Blåsippa
 Bäckbräsma
+Kransmossa
 Spillkråka</t>
         </is>
       </c>
@@ -756,7 +757,7 @@
         <v>45996</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -894,7 +895,7 @@
         <v>44655</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1032,7 +1033,7 @@
         <v>46197</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1161,7 +1162,7 @@
         <v>45180</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1292,7 +1293,7 @@
         <v>46033</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1422,7 +1423,7 @@
         <v>45628</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1555,7 +1556,7 @@
         <v>45239</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1683,7 +1684,7 @@
         <v>46033</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1809,7 +1810,7 @@
         <v>44502</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1935,7 +1936,7 @@
         <v>45527</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2062,7 +2063,7 @@
         <v>45527</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2185,7 +2186,7 @@
         <v>45940</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2312,7 +2313,7 @@
         <v>45616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2431,7 +2432,7 @@
         <v>45919</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2554,7 +2555,7 @@
         <v>46150</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2673,7 +2674,7 @@
         <v>45527</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2796,7 +2797,7 @@
         <v>46078</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2918,7 +2919,7 @@
         <v>46020</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3039,7 +3040,7 @@
         <v>46178</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3161,7 +3162,7 @@
         <v>45961</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3282,7 +3283,7 @@
         <v>45702</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3404,7 +3405,7 @@
         <v>45301</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3520,7 +3521,7 @@
         <v>46251</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3641,7 +3642,7 @@
         <v>45527</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3762,7 +3763,7 @@
         <v>45887</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3873,7 +3874,7 @@
         <v>45469</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3988,7 +3989,7 @@
         <v>45897</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4107,7 +4108,7 @@
         <v>44489</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4225,7 +4226,7 @@
         <v>46033</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4343,7 +4344,7 @@
         <v>46055</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4457,7 +4458,7 @@
         <v>46178</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4572,7 +4573,7 @@
         <v>45702</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4691,7 +4692,7 @@
         <v>46062</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4810,7 +4811,7 @@
         <v>44588</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4928,7 +4929,7 @@
         <v>46033</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5041,7 +5042,7 @@
         <v>46198</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5154,7 +5155,7 @@
         <v>46198</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5271,7 +5272,7 @@
         <v>46239</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5389,7 +5390,7 @@
         <v>44502</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5501,7 +5502,7 @@
         <v>46048</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5613,7 +5614,7 @@
         <v>45252</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5730,7 +5731,7 @@
         <v>46051</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5842,7 +5843,7 @@
         <v>45565</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5958,7 +5959,7 @@
         <v>46051</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6065,7 +6066,7 @@
         <v>45933</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6181,7 +6182,7 @@
         <v>44582</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6292,7 +6293,7 @@
         <v>45664</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6407,7 +6408,7 @@
         <v>44579</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6518,7 +6519,7 @@
         <v>46239</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6634,7 +6635,7 @@
         <v>44961</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6741,7 +6742,7 @@
         <v>44550</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6857,7 +6858,7 @@
         <v>44523</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6968,7 +6969,7 @@
         <v>44945</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7074,7 +7075,7 @@
         <v>46070</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7184,7 +7185,7 @@
         <v>44883</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7299,7 +7300,7 @@
         <v>45642</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7414,7 +7415,7 @@
         <v>45527</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7525,7 +7526,7 @@
         <v>46000</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7636,7 +7637,7 @@
         <v>46146</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7747,7 +7748,7 @@
         <v>45171</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7858,7 +7859,7 @@
         <v>46157</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7969,7 +7970,7 @@
         <v>45821</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8084,7 +8085,7 @@
         <v>45825</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8199,7 +8200,7 @@
         <v>46176</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8310,7 +8311,7 @@
         <v>46177</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8421,7 +8422,7 @@
         <v>46178</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8536,7 +8537,7 @@
         <v>46178</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8651,7 +8652,7 @@
         <v>46185</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8766,7 +8767,7 @@
         <v>45670</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8876,7 +8877,7 @@
         <v>46240</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8987,7 +8988,7 @@
         <v>45001</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9093,7 +9094,7 @@
         <v>44550</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9204,7 +9205,7 @@
         <v>44585</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9315,7 +9316,7 @@
         <v>45317</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9430,7 +9431,7 @@
         <v>44880</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9544,7 +9545,7 @@
         <v>44574</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9654,7 +9655,7 @@
         <v>44880</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9768,7 +9769,7 @@
         <v>44864</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9882,7 +9883,7 @@
         <v>45889</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9996,7 +9997,7 @@
         <v>45743</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10106,7 +10107,7 @@
         <v>45008</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10215,7 +10216,7 @@
         <v>45441</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10320,7 +10321,7 @@
         <v>46062</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10429,7 +10430,7 @@
         <v>45842</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10539,7 +10540,7 @@
         <v>45818</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10649,7 +10650,7 @@
         <v>45818</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10759,7 +10760,7 @@
         <v>45743</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10869,7 +10870,7 @@
         <v>45743</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10979,7 +10980,7 @@
         <v>45767</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11089,7 +11090,7 @@
         <v>46105</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11199,7 +11200,7 @@
         <v>46164</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11309,7 +11310,7 @@
         <v>45933</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11419,7 +11420,7 @@
         <v>46177</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11529,7 +11530,7 @@
         <v>45275</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11638,7 +11639,7 @@
         <v>45610</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11752,7 +11753,7 @@
         <v>46204</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11861,7 +11862,7 @@
         <v>46212</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11971,7 +11972,7 @@
         <v>46213</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12080,7 +12081,7 @@
         <v>46266</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12190,7 +12191,7 @@
         <v>45763</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12295,7 +12296,7 @@
         <v>44918</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12400,7 +12401,7 @@
         <v>45226</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12514,7 +12515,7 @@
         <v>45615</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12624,7 +12625,7 @@
         <v>44680</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12729,7 +12730,7 @@
         <v>45757</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12834,7 +12835,7 @@
         <v>46245</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12944,7 +12945,7 @@
         <v>46199</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13054,7 +13055,7 @@
         <v>46296</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13164,7 +13165,7 @@
         <v>45319</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13282,7 +13283,7 @@
         <v>45316</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13396,7 +13397,7 @@
         <v>44550</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13506,7 +13507,7 @@
         <v>46069</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13616,7 +13617,7 @@
         <v>44523</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13694,7 +13695,7 @@
         <v>44565</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13767,7 +13768,7 @@
         <v>44783</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13840,7 +13841,7 @@
         <v>44846</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13918,7 +13919,7 @@
         <v>44802</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13991,7 +13992,7 @@
         <v>44698</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14064,7 +14065,7 @@
         <v>44529</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14137,7 +14138,7 @@
         <v>44588</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14215,7 +14216,7 @@
         <v>44817</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14293,7 +14294,7 @@
         <v>44491</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14366,7 +14367,7 @@
         <v>44741</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14439,7 +14440,7 @@
         <v>44720</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14512,7 +14513,7 @@
         <v>44502</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14590,7 +14591,7 @@
         <v>44746</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14663,7 +14664,7 @@
         <v>44859</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14741,7 +14742,7 @@
         <v>44495</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14814,7 +14815,7 @@
         <v>44575</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14887,7 +14888,7 @@
         <v>45170</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14960,7 +14961,7 @@
         <v>45022</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15038,7 +15039,7 @@
         <v>45459</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15111,7 +15112,7 @@
         <v>44628</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15189,7 +15190,7 @@
         <v>45175</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15262,7 +15263,7 @@
         <v>44900</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15335,7 +15336,7 @@
         <v>45603</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15408,7 +15409,7 @@
         <v>44532</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15481,7 +15482,7 @@
         <v>46007</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15554,7 +15555,7 @@
         <v>45905</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15632,7 +15633,7 @@
         <v>45541</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15710,7 +15711,7 @@
         <v>45558</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15783,7 +15784,7 @@
         <v>45889</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15861,7 +15862,7 @@
         <v>46020</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15934,7 +15935,7 @@
         <v>45889</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16012,7 +16013,7 @@
         <v>46021</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16085,7 +16086,7 @@
         <v>45342</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16158,7 +16159,7 @@
         <v>46020</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16231,7 +16232,7 @@
         <v>45940</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16309,7 +16310,7 @@
         <v>44956</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16387,7 +16388,7 @@
         <v>45895</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16465,7 +16466,7 @@
         <v>45770</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16538,7 +16539,7 @@
         <v>45770</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16611,7 +16612,7 @@
         <v>46030</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16684,7 +16685,7 @@
         <v>46035</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16757,7 +16758,7 @@
         <v>46033</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16830,7 +16831,7 @@
         <v>46034</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16903,7 +16904,7 @@
         <v>44805</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16981,7 +16982,7 @@
         <v>46036</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17059,7 +17060,7 @@
         <v>46037</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17132,7 +17133,7 @@
         <v>45980</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17210,7 +17211,7 @@
         <v>45906</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17288,7 +17289,7 @@
         <v>46043</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17361,7 +17362,7 @@
         <v>45462</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17439,7 +17440,7 @@
         <v>46032</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17512,7 +17513,7 @@
         <v>46044</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17585,7 +17586,7 @@
         <v>45799</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17658,7 +17659,7 @@
         <v>45429</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17731,7 +17732,7 @@
         <v>46051</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17804,7 +17805,7 @@
         <v>46051</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17877,7 +17878,7 @@
         <v>46050</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17950,7 +17951,7 @@
         <v>46051</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18023,7 +18024,7 @@
         <v>45070</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18096,7 +18097,7 @@
         <v>45407</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18174,7 +18175,7 @@
         <v>45252</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18247,7 +18248,7 @@
         <v>45260</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18320,7 +18321,7 @@
         <v>46048</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18393,7 +18394,7 @@
         <v>45569</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18466,7 +18467,7 @@
         <v>45933</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18539,7 +18540,7 @@
         <v>46066</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18617,7 +18618,7 @@
         <v>45610</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18695,7 +18696,7 @@
         <v>45701</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18768,7 +18769,7 @@
         <v>45694</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18841,7 +18842,7 @@
         <v>45429</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18914,7 +18915,7 @@
         <v>46072</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18987,7 +18988,7 @@
         <v>46072</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19060,7 +19061,7 @@
         <v>46072</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19133,7 +19134,7 @@
         <v>45218</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19206,7 +19207,7 @@
         <v>45989</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19284,7 +19285,7 @@
         <v>45230</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19357,7 +19358,7 @@
         <v>45230</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19430,7 +19431,7 @@
         <v>45995</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19508,7 +19509,7 @@
         <v>45951</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19581,7 +19582,7 @@
         <v>45951</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19654,7 +19655,7 @@
         <v>45708</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19727,7 +19728,7 @@
         <v>45099</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19800,7 +19801,7 @@
         <v>46084</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19873,7 +19874,7 @@
         <v>45953</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19951,7 +19952,7 @@
         <v>45952</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20024,7 +20025,7 @@
         <v>46090</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20097,7 +20098,7 @@
         <v>45963</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20170,7 +20171,7 @@
         <v>44783</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20243,7 +20244,7 @@
         <v>45840</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20321,7 +20322,7 @@
         <v>45792</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20399,7 +20400,7 @@
         <v>45784</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20477,7 +20478,7 @@
         <v>44757</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20555,7 +20556,7 @@
         <v>45230</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20628,7 +20629,7 @@
         <v>46094</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20701,7 +20702,7 @@
         <v>44501</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20774,7 +20775,7 @@
         <v>46098</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20852,7 +20853,7 @@
         <v>46098</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20930,7 +20931,7 @@
         <v>45933</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21003,7 +21004,7 @@
         <v>45216</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21076,7 +21077,7 @@
         <v>46098</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21154,7 +21155,7 @@
         <v>45968</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21227,7 +21228,7 @@
         <v>46098</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21300,7 +21301,7 @@
         <v>45840</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21378,7 +21379,7 @@
         <v>46098</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21451,7 +21452,7 @@
         <v>45889</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21529,7 +21530,7 @@
         <v>46099</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21602,7 +21603,7 @@
         <v>46099</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21680,7 +21681,7 @@
         <v>45971</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21753,7 +21754,7 @@
         <v>45973</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21831,7 +21832,7 @@
         <v>45350</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21904,7 +21905,7 @@
         <v>45818</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21982,7 +21983,7 @@
         <v>45975</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22055,7 +22056,7 @@
         <v>45818</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22133,7 +22134,7 @@
         <v>46105</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22211,7 +22212,7 @@
         <v>46105</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22289,7 +22290,7 @@
         <v>46108</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22362,7 +22363,7 @@
         <v>46111</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22435,7 +22436,7 @@
         <v>46111</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22508,7 +22509,7 @@
         <v>45880</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22586,7 +22587,7 @@
         <v>46119</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22664,7 +22665,7 @@
         <v>45880</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22742,7 +22743,7 @@
         <v>44792</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22815,7 +22816,7 @@
         <v>46122</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22893,7 +22894,7 @@
         <v>46124</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22971,7 +22972,7 @@
         <v>46125</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23044,7 +23045,7 @@
         <v>46125</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23117,7 +23118,7 @@
         <v>46128</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23195,7 +23196,7 @@
         <v>46128</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23273,7 +23274,7 @@
         <v>45827</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23346,7 +23347,7 @@
         <v>46132</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23424,7 +23425,7 @@
         <v>46134</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23502,7 +23503,7 @@
         <v>46134</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23575,7 +23576,7 @@
         <v>45253</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23648,7 +23649,7 @@
         <v>45316</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23721,7 +23722,7 @@
         <v>46139</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23799,7 +23800,7 @@
         <v>45230</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23872,7 +23873,7 @@
         <v>45840</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23950,7 +23951,7 @@
         <v>45840</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24028,7 +24029,7 @@
         <v>46136</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24106,7 +24107,7 @@
         <v>45484</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24184,7 +24185,7 @@
         <v>45209</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24257,7 +24258,7 @@
         <v>45848</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24330,7 +24331,7 @@
         <v>46056</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24403,7 +24404,7 @@
         <v>46069</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24476,7 +24477,7 @@
         <v>46020</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24549,7 +24550,7 @@
         <v>44750</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24627,7 +24628,7 @@
         <v>45895</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24700,7 +24701,7 @@
         <v>45287</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24773,7 +24774,7 @@
         <v>45810</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24846,7 +24847,7 @@
         <v>45743</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24924,7 +24925,7 @@
         <v>45623</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24997,7 +24998,7 @@
         <v>45551</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25075,7 +25076,7 @@
         <v>44914</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25148,7 +25149,7 @@
         <v>46083</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25221,7 +25222,7 @@
         <v>45866</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25294,7 +25295,7 @@
         <v>45566</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25372,7 +25373,7 @@
         <v>45505</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25445,7 +25446,7 @@
         <v>45866</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25523,7 +25524,7 @@
         <v>45538</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25596,7 +25597,7 @@
         <v>45867</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25669,7 +25670,7 @@
         <v>45729</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25742,7 +25743,7 @@
         <v>46034</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25815,7 +25816,7 @@
         <v>45626</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25893,7 +25894,7 @@
         <v>45743</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25966,7 +25967,7 @@
         <v>45729</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26039,7 +26040,7 @@
         <v>45583</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26112,7 +26113,7 @@
         <v>45576</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26185,7 +26186,7 @@
         <v>45469</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26258,7 +26259,7 @@
         <v>45172</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26336,7 +26337,7 @@
         <v>44472</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26414,7 +26415,7 @@
         <v>46157</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26492,7 +26493,7 @@
         <v>46114</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26570,7 +26571,7 @@
         <v>45630</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26643,7 +26644,7 @@
         <v>45190</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26721,7 +26722,7 @@
         <v>46161</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26794,7 +26795,7 @@
         <v>44662</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26872,7 +26873,7 @@
         <v>45061</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26950,7 +26951,7 @@
         <v>46163</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27023,7 +27024,7 @@
         <v>45702</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27096,7 +27097,7 @@
         <v>46164</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27174,7 +27175,7 @@
         <v>46167</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27252,7 +27253,7 @@
         <v>45230</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27325,7 +27326,7 @@
         <v>45610</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27403,7 +27404,7 @@
         <v>46169</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27481,7 +27482,7 @@
         <v>46169</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27559,7 +27560,7 @@
         <v>45756</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27632,7 +27633,7 @@
         <v>44817</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27710,7 +27711,7 @@
         <v>46174</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27788,7 +27789,7 @@
         <v>45784</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27866,7 +27867,7 @@
         <v>45278</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27939,7 +27940,7 @@
         <v>46174</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28017,7 +28018,7 @@
         <v>45233</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28090,7 +28091,7 @@
         <v>45268</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28163,7 +28164,7 @@
         <v>45268</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28236,7 +28237,7 @@
         <v>46062</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28309,7 +28310,7 @@
         <v>45070</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28382,7 +28383,7 @@
         <v>46030</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28455,7 +28456,7 @@
         <v>46177</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28533,7 +28534,7 @@
         <v>46177</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28611,7 +28612,7 @@
         <v>46178</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28689,7 +28690,7 @@
         <v>46136</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28767,7 +28768,7 @@
         <v>46099</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28840,7 +28841,7 @@
         <v>46114</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28918,7 +28919,7 @@
         <v>46136</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28996,7 +28997,7 @@
         <v>45940</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29074,7 +29075,7 @@
         <v>45920</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29152,7 +29153,7 @@
         <v>46136</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29230,7 +29231,7 @@
         <v>45534</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29308,7 +29309,7 @@
         <v>46178</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29386,7 +29387,7 @@
         <v>46033</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29459,7 +29460,7 @@
         <v>45919</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29537,7 +29538,7 @@
         <v>45943</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29610,7 +29611,7 @@
         <v>46183</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29688,7 +29689,7 @@
         <v>46148</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29766,7 +29767,7 @@
         <v>46185</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29844,7 +29845,7 @@
         <v>45615</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29922,7 +29923,7 @@
         <v>45474</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30000,7 +30001,7 @@
         <v>46198</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30078,7 +30079,7 @@
         <v>45474</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30156,7 +30157,7 @@
         <v>45617</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30234,7 +30235,7 @@
         <v>45610</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30312,7 +30313,7 @@
         <v>45254</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30385,7 +30386,7 @@
         <v>45541</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30463,7 +30464,7 @@
         <v>45350</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30536,7 +30537,7 @@
         <v>44546</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30609,7 +30610,7 @@
         <v>46212</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30687,7 +30688,7 @@
         <v>46212</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30765,7 +30766,7 @@
         <v>46255</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30843,7 +30844,7 @@
         <v>46255</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30921,7 +30922,7 @@
         <v>46255</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30999,7 +31000,7 @@
         <v>45086</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31077,7 +31078,7 @@
         <v>45104</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31155,7 +31156,7 @@
         <v>46262</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31228,7 +31229,7 @@
         <v>44917</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31301,7 +31302,7 @@
         <v>46266</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31379,7 +31380,7 @@
         <v>46225</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31457,7 +31458,7 @@
         <v>46266</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31535,7 +31536,7 @@
         <v>45267</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31608,7 +31609,7 @@
         <v>44574</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31686,7 +31687,7 @@
         <v>45509</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31759,7 +31760,7 @@
         <v>46273</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31837,7 +31838,7 @@
         <v>45743</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31910,7 +31911,7 @@
         <v>45296</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31983,7 +31984,7 @@
         <v>45163</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32061,7 +32062,7 @@
         <v>46279</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32139,7 +32140,7 @@
         <v>46279</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32217,7 +32218,7 @@
         <v>45239</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32295,7 +32296,7 @@
         <v>46167</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32373,7 +32374,7 @@
         <v>46279</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32451,7 +32452,7 @@
         <v>45748</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32524,7 +32525,7 @@
         <v>46281</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32602,7 +32603,7 @@
         <v>46281</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32680,7 +32681,7 @@
         <v>46281</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32758,7 +32759,7 @@
         <v>46281</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32836,7 +32837,7 @@
         <v>46281</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32909,7 +32910,7 @@
         <v>46240</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32982,7 +32983,7 @@
         <v>46240</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33055,7 +33056,7 @@
         <v>45615</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33133,7 +33134,7 @@
         <v>46281</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33211,7 +33212,7 @@
         <v>46282</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33284,7 +33285,7 @@
         <v>46239</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33362,7 +33363,7 @@
         <v>45573</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33440,7 +33441,7 @@
         <v>45573</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33518,7 +33519,7 @@
         <v>46281</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33596,7 +33597,7 @@
         <v>45551</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33674,7 +33675,7 @@
         <v>44575</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33747,7 +33748,7 @@
         <v>45757</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33820,7 +33821,7 @@
         <v>44733</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33893,7 +33894,7 @@
         <v>44911</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33966,7 +33967,7 @@
         <v>46286</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34039,7 +34040,7 @@
         <v>45278</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34112,7 +34113,7 @@
         <v>46244</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34185,7 +34186,7 @@
         <v>46058</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34258,7 +34259,7 @@
         <v>44495</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34331,7 +34332,7 @@
         <v>46199</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34409,7 +34410,7 @@
         <v>46178</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34487,7 +34488,7 @@
         <v>45957</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34560,7 +34561,7 @@
         <v>45268</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34633,7 +34634,7 @@
         <v>45958</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34711,7 +34712,7 @@
         <v>45958</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34789,7 +34790,7 @@
         <v>46290</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34867,7 +34868,7 @@
         <v>45086</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34945,7 +34946,7 @@
         <v>44509</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35018,7 +35019,7 @@
         <v>46174</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35096,7 +35097,7 @@
         <v>45358</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35169,7 +35170,7 @@
         <v>45239</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35247,7 +35248,7 @@
         <v>45757</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35320,7 +35321,7 @@
         <v>46296</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35398,7 +35399,7 @@
         <v>45541</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35476,7 +35477,7 @@
         <v>45701</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35549,7 +35550,7 @@
         <v>44909</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35622,7 +35623,7 @@
         <v>45194</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35695,7 +35696,7 @@
         <v>45173</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35773,7 +35774,7 @@
         <v>45055</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35851,7 +35852,7 @@
         <v>44529</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35924,7 +35925,7 @@
         <v>45113</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36002,7 +36003,7 @@
         <v>45111</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36080,7 +36081,7 @@
         <v>45278</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36153,7 +36154,7 @@
         <v>45590</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36226,7 +36227,7 @@
         <v>45187</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36304,7 +36305,7 @@
         <v>45337</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36377,7 +36378,7 @@
         <v>44102</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36455,7 +36456,7 @@
         <v>45700</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36533,7 +36534,7 @@
         <v>45700</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36611,7 +36612,7 @@
         <v>44550</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36689,7 +36690,7 @@
         <v>45317</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36767,7 +36768,7 @@
         <v>45316</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36845,7 +36846,7 @@
         <v>44671</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36923,7 +36924,7 @@
         <v>45720</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37001,7 +37002,7 @@
         <v>45706</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37079,7 +37080,7 @@
         <v>45906</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37157,7 +37158,7 @@
         <v>45989</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37235,7 +37236,7 @@
         <v>45995</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37313,7 +37314,7 @@
         <v>46070</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37391,7 +37392,7 @@
         <v>45700</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37469,7 +37470,7 @@
         <v>46142</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37547,7 +37548,7 @@
         <v>46125</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37625,7 +37626,7 @@
         <v>45971</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37698,7 +37699,7 @@
         <v>46085</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>

--- a/Översikt HEDEMORA.xlsx
+++ b/Översikt HEDEMORA.xlsx
@@ -601,7 +601,7 @@
         <v>45105</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>45996</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>44655</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>46197</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>45180</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>46033</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>45628</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>45239</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>46033</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>44502</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>45527</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>45527</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>45940</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>45616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>45919</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>46150</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>45527</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>46078</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>46020</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>46178</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>45961</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>45702</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>45301</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         <v>46251</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>45527</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>45887</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>45469</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>45897</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>44489</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>46033</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>46055</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>46178</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>45702</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>46062</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>44588</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>46033</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>46198</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>46198</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>46239</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>44502</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>46048</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>45252</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>46051</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>45565</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>46051</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>45933</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>44582</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>45664</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>44579</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>46239</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         <v>44961</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6742,7 +6742,7 @@
         <v>44550</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         <v>44523</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         <v>44945</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         <v>46070</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>44883</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         <v>45642</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>45527</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
         <v>46000</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         <v>46146</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         <v>45171</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>46157</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         <v>45821</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>45825</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>46176</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>46177</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>46178</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>46178</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>46185</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8767,7 +8767,7 @@
         <v>45670</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>46240</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>45001</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>44550</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         <v>44585</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>45317</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>44880</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>44574</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         <v>44880</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9769,7 +9769,7 @@
         <v>44864</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>45889</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9997,7 +9997,7 @@
         <v>45743</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         <v>45008</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>45441</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
         <v>46062</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>45842</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>45818</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10650,7 +10650,7 @@
         <v>45818</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>45743</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         <v>45743</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>45767</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11090,7 +11090,7 @@
         <v>46105</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11200,7 +11200,7 @@
         <v>46164</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>45933</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11420,7 +11420,7 @@
         <v>46177</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>45275</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>45610</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>46204</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>46212</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11972,7 +11972,7 @@
         <v>46213</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12081,7 +12081,7 @@
         <v>46266</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12191,7 +12191,7 @@
         <v>45763</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12296,7 +12296,7 @@
         <v>44918</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
         <v>45226</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>45615</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>44680</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>45757</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>46245</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12945,7 +12945,7 @@
         <v>46199</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>46296</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13165,7 +13165,7 @@
         <v>45319</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>45316</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>44550</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13507,7 +13507,7 @@
         <v>46069</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13617,7 +13617,7 @@
         <v>44523</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13695,7 +13695,7 @@
         <v>44565</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>44783</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>44846</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13919,7 +13919,7 @@
         <v>44802</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>44698</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14065,7 +14065,7 @@
         <v>44529</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14138,7 +14138,7 @@
         <v>44588</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>44817</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>44491</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14367,7 +14367,7 @@
         <v>44741</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>44720</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         <v>44502</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14591,7 +14591,7 @@
         <v>44746</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>44859</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14742,7 +14742,7 @@
         <v>44495</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>44575</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14888,7 +14888,7 @@
         <v>45170</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         <v>45022</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>45459</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>44628</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15190,7 +15190,7 @@
         <v>45175</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>44900</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>45603</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15409,7 +15409,7 @@
         <v>44532</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15482,7 +15482,7 @@
         <v>46007</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>45905</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         <v>45541</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15711,7 +15711,7 @@
         <v>45558</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15784,7 +15784,7 @@
         <v>45889</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15862,7 +15862,7 @@
         <v>46020</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15935,7 +15935,7 @@
         <v>45889</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>46021</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>45342</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>46020</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>45940</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16310,7 +16310,7 @@
         <v>44956</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16388,7 +16388,7 @@
         <v>45895</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16466,7 +16466,7 @@
         <v>45770</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16539,7 +16539,7 @@
         <v>45770</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16612,7 +16612,7 @@
         <v>46030</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16685,7 +16685,7 @@
         <v>46035</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>46033</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16831,7 +16831,7 @@
         <v>46034</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         <v>44805</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>46036</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>46037</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>45980</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>45906</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>46043</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>45462</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17440,7 +17440,7 @@
         <v>46032</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17513,7 +17513,7 @@
         <v>46044</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
         <v>45799</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17659,7 +17659,7 @@
         <v>45429</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>46051</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>46051</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>46050</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17951,7 +17951,7 @@
         <v>46051</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18024,7 +18024,7 @@
         <v>45070</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18097,7 +18097,7 @@
         <v>45407</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>45252</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18248,7 +18248,7 @@
         <v>45260</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>46048</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18394,7 +18394,7 @@
         <v>45569</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18467,7 +18467,7 @@
         <v>45933</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>46066</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18618,7 +18618,7 @@
         <v>45610</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>45701</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18769,7 +18769,7 @@
         <v>45694</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18842,7 +18842,7 @@
         <v>45429</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18915,7 +18915,7 @@
         <v>46072</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>46072</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19061,7 +19061,7 @@
         <v>46072</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19134,7 +19134,7 @@
         <v>45218</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
         <v>45989</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>45230</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>45230</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19431,7 +19431,7 @@
         <v>45995</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19509,7 +19509,7 @@
         <v>45951</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19582,7 +19582,7 @@
         <v>45951</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19655,7 +19655,7 @@
         <v>45708</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>45099</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19801,7 +19801,7 @@
         <v>46084</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>45953</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19952,7 +19952,7 @@
         <v>45952</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20025,7 +20025,7 @@
         <v>46090</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20098,7 +20098,7 @@
         <v>45963</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20171,7 +20171,7 @@
         <v>44783</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20244,7 +20244,7 @@
         <v>45840</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20322,7 +20322,7 @@
         <v>45792</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20400,7 +20400,7 @@
         <v>45784</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>44757</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20556,7 +20556,7 @@
         <v>45230</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20629,7 +20629,7 @@
         <v>46094</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20702,7 +20702,7 @@
         <v>44501</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20775,7 +20775,7 @@
         <v>46098</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>46098</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20931,7 +20931,7 @@
         <v>45933</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21004,7 +21004,7 @@
         <v>45216</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21077,7 +21077,7 @@
         <v>46098</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21155,7 +21155,7 @@
         <v>45968</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>46098</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>45840</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>46098</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>45889</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21530,7 +21530,7 @@
         <v>46099</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>46099</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21681,7 +21681,7 @@
         <v>45971</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21754,7 +21754,7 @@
         <v>45973</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         <v>45350</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21905,7 +21905,7 @@
         <v>45818</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>45975</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>45818</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>46105</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22212,7 +22212,7 @@
         <v>46105</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         <v>46108</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22363,7 +22363,7 @@
         <v>46111</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22436,7 +22436,7 @@
         <v>46111</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22509,7 +22509,7 @@
         <v>45880</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>46119</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22665,7 +22665,7 @@
         <v>45880</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22743,7 +22743,7 @@
         <v>44792</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>46122</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22894,7 +22894,7 @@
         <v>46124</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>46125</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23045,7 +23045,7 @@
         <v>46125</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23118,7 +23118,7 @@
         <v>46128</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23196,7 +23196,7 @@
         <v>46128</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23274,7 +23274,7 @@
         <v>45827</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23347,7 +23347,7 @@
         <v>46132</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23425,7 +23425,7 @@
         <v>46134</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>46134</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23576,7 +23576,7 @@
         <v>45253</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23649,7 +23649,7 @@
         <v>45316</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23722,7 +23722,7 @@
         <v>46139</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>45230</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>45840</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>45840</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24029,7 +24029,7 @@
         <v>46136</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24107,7 +24107,7 @@
         <v>45484</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24185,7 +24185,7 @@
         <v>45209</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24258,7 +24258,7 @@
         <v>45848</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24331,7 +24331,7 @@
         <v>46056</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
         <v>46069</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>46020</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>44750</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24628,7 +24628,7 @@
         <v>45895</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24701,7 +24701,7 @@
         <v>45287</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24774,7 +24774,7 @@
         <v>45810</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24847,7 +24847,7 @@
         <v>45743</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24925,7 +24925,7 @@
         <v>45623</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24998,7 +24998,7 @@
         <v>45551</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25076,7 +25076,7 @@
         <v>44914</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>46083</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25222,7 +25222,7 @@
         <v>45866</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>45566</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25373,7 +25373,7 @@
         <v>45505</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25446,7 +25446,7 @@
         <v>45866</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25524,7 +25524,7 @@
         <v>45538</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25597,7 +25597,7 @@
         <v>45867</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25670,7 +25670,7 @@
         <v>45729</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25743,7 +25743,7 @@
         <v>46034</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25816,7 +25816,7 @@
         <v>45626</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25894,7 +25894,7 @@
         <v>45743</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25967,7 +25967,7 @@
         <v>45729</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26040,7 +26040,7 @@
         <v>45583</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26113,7 +26113,7 @@
         <v>45576</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26186,7 +26186,7 @@
         <v>45469</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26259,7 +26259,7 @@
         <v>45172</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
         <v>44472</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>46157</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26493,7 +26493,7 @@
         <v>46114</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26571,7 +26571,7 @@
         <v>45630</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>45190</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26722,7 +26722,7 @@
         <v>46161</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26795,7 +26795,7 @@
         <v>44662</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26873,7 +26873,7 @@
         <v>45061</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26951,7 +26951,7 @@
         <v>46163</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27024,7 +27024,7 @@
         <v>45702</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27097,7 +27097,7 @@
         <v>46164</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27175,7 +27175,7 @@
         <v>46167</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27253,7 +27253,7 @@
         <v>45230</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27326,7 +27326,7 @@
         <v>45610</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27404,7 +27404,7 @@
         <v>46169</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27482,7 +27482,7 @@
         <v>46169</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27560,7 +27560,7 @@
         <v>45756</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27633,7 +27633,7 @@
         <v>44817</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27711,7 +27711,7 @@
         <v>46174</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27789,7 +27789,7 @@
         <v>45784</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27867,7 +27867,7 @@
         <v>45278</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27940,7 +27940,7 @@
         <v>46174</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28018,7 +28018,7 @@
         <v>45233</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28091,7 +28091,7 @@
         <v>45268</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28164,7 +28164,7 @@
         <v>45268</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28237,7 +28237,7 @@
         <v>46062</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>45070</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28383,7 +28383,7 @@
         <v>46030</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28456,7 +28456,7 @@
         <v>46177</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28534,7 +28534,7 @@
         <v>46177</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28612,7 +28612,7 @@
         <v>46178</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28690,7 +28690,7 @@
         <v>46136</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>46099</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>46114</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28919,7 +28919,7 @@
         <v>46136</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
         <v>45940</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29075,7 +29075,7 @@
         <v>45920</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29153,7 +29153,7 @@
         <v>46136</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29231,7 +29231,7 @@
         <v>45534</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>46178</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29387,7 +29387,7 @@
         <v>46033</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29460,7 +29460,7 @@
         <v>45919</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29538,7 +29538,7 @@
         <v>45943</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>46183</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29689,7 +29689,7 @@
         <v>46148</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29767,7 +29767,7 @@
         <v>46185</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29845,7 +29845,7 @@
         <v>45615</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29923,7 +29923,7 @@
         <v>45474</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30001,7 +30001,7 @@
         <v>46198</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30079,7 +30079,7 @@
         <v>45474</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30157,7 +30157,7 @@
         <v>45617</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30235,7 +30235,7 @@
         <v>45610</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30313,7 +30313,7 @@
         <v>45254</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30386,7 +30386,7 @@
         <v>45541</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30464,7 +30464,7 @@
         <v>45350</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30537,7 +30537,7 @@
         <v>44546</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30610,7 +30610,7 @@
         <v>46212</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30688,7 +30688,7 @@
         <v>46212</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30766,7 +30766,7 @@
         <v>46255</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30844,7 +30844,7 @@
         <v>46255</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30922,7 +30922,7 @@
         <v>46255</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31000,7 +31000,7 @@
         <v>45086</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31078,7 +31078,7 @@
         <v>45104</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>46262</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31229,7 +31229,7 @@
         <v>44917</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31302,7 +31302,7 @@
         <v>46266</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>46225</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31458,7 +31458,7 @@
         <v>46266</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>45267</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31609,7 +31609,7 @@
         <v>44574</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>45509</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31760,7 +31760,7 @@
         <v>46273</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31838,7 +31838,7 @@
         <v>45743</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31911,7 +31911,7 @@
         <v>45296</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31984,7 +31984,7 @@
         <v>45163</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32062,7 +32062,7 @@
         <v>46279</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32140,7 +32140,7 @@
         <v>46279</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32218,7 +32218,7 @@
         <v>45239</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32296,7 +32296,7 @@
         <v>46167</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>46279</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>45748</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>46281</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>46281</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         <v>46281</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>46281</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32837,7 +32837,7 @@
         <v>46281</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32910,7 +32910,7 @@
         <v>46240</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32983,7 +32983,7 @@
         <v>46240</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33056,7 +33056,7 @@
         <v>45615</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33134,7 +33134,7 @@
         <v>46281</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33212,7 +33212,7 @@
         <v>46282</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33285,7 +33285,7 @@
         <v>46239</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33363,7 +33363,7 @@
         <v>45573</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33441,7 +33441,7 @@
         <v>45573</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33519,7 +33519,7 @@
         <v>46281</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33597,7 +33597,7 @@
         <v>45551</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33675,7 +33675,7 @@
         <v>44575</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>45757</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         <v>44733</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33894,7 +33894,7 @@
         <v>44911</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33967,7 +33967,7 @@
         <v>46286</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34040,7 +34040,7 @@
         <v>45278</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34113,7 +34113,7 @@
         <v>46244</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34186,7 +34186,7 @@
         <v>46058</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34259,7 +34259,7 @@
         <v>44495</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34332,7 +34332,7 @@
         <v>46199</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34410,7 +34410,7 @@
         <v>46178</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>45957</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34561,7 +34561,7 @@
         <v>45268</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>45958</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34712,7 +34712,7 @@
         <v>45958</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34790,7 +34790,7 @@
         <v>46290</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34868,7 +34868,7 @@
         <v>45086</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34946,7 +34946,7 @@
         <v>44509</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35019,7 +35019,7 @@
         <v>46174</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35097,7 +35097,7 @@
         <v>45358</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35170,7 +35170,7 @@
         <v>45239</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35248,7 +35248,7 @@
         <v>45757</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35321,7 +35321,7 @@
         <v>46296</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35399,7 +35399,7 @@
         <v>45541</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35477,7 +35477,7 @@
         <v>45701</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35550,7 +35550,7 @@
         <v>44909</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35623,7 +35623,7 @@
         <v>45194</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35696,7 +35696,7 @@
         <v>45173</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35774,7 +35774,7 @@
         <v>45055</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35852,7 +35852,7 @@
         <v>44529</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35925,7 +35925,7 @@
         <v>45113</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36003,7 +36003,7 @@
         <v>45111</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36081,7 +36081,7 @@
         <v>45278</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36154,7 +36154,7 @@
         <v>45590</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36227,7 +36227,7 @@
         <v>45187</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36305,7 +36305,7 @@
         <v>45337</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36378,7 +36378,7 @@
         <v>44102</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36456,7 +36456,7 @@
         <v>45700</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36534,7 +36534,7 @@
         <v>45700</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36612,7 +36612,7 @@
         <v>44550</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36690,7 +36690,7 @@
         <v>45317</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>45316</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36846,7 +36846,7 @@
         <v>44671</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36924,7 +36924,7 @@
         <v>45720</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37002,7 +37002,7 @@
         <v>45706</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37080,7 +37080,7 @@
         <v>45906</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37158,7 +37158,7 @@
         <v>45989</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37236,7 +37236,7 @@
         <v>45995</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37314,7 +37314,7 @@
         <v>46070</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37392,7 +37392,7 @@
         <v>45700</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37470,7 +37470,7 @@
         <v>46142</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37548,7 +37548,7 @@
         <v>46125</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37626,7 +37626,7 @@
         <v>45971</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>46085</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>

--- a/Översikt HEDEMORA.xlsx
+++ b/Översikt HEDEMORA.xlsx
@@ -601,7 +601,7 @@
         <v>45105</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>45996</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>44655</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>46197</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>45180</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>46033</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>45239</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>45628</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>45527</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>45527</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>46033</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>44502</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>45940</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>45616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>45919</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>46150</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>45527</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>46078</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>46020</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>46178</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>45961</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>45702</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>45527</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>45301</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>46251</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>45887</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>45469</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>45897</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>44489</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>46033</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>46055</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>46178</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>45702</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>46062</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>44588</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>46033</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>46198</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>46198</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>46239</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>44502</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>46048</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>46051</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>44579</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>45664</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>45933</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44961</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>45565</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>46051</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>44582</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>46239</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>44550</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>44523</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>45527</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>44883</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7078,7 +7078,7 @@
         <v>45642</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>45821</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>45825</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7423,7 +7423,7 @@
         <v>46000</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>45171</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         <v>44945</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>46146</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         <v>46070</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>46157</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>46177</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>46176</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>46178</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         <v>46178</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>46185</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>45670</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8760,7 +8760,7 @@
         <v>46240</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8871,7 +8871,7 @@
         <v>45001</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>44550</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>44585</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>45317</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>44880</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>44574</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>44864</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>44880</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>45757</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
         <v>45889</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>44918</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>45275</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>45743</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         <v>45226</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10423,7 +10423,7 @@
         <v>45842</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>45818</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         <v>45818</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10753,7 +10753,7 @@
         <v>44680</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>45610</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10972,7 +10972,7 @@
         <v>45743</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>45743</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11192,7 +11192,7 @@
         <v>45767</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>45763</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11407,7 +11407,7 @@
         <v>45615</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>46062</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         <v>45441</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>45008</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
         <v>46105</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         <v>46164</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>46177</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>45933</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>46204</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12389,7 +12389,7 @@
         <v>46212</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
         <v>46213</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12608,7 +12608,7 @@
         <v>46266</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
         <v>46245</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>46296</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12938,7 +12938,7 @@
         <v>44550</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>45319</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
         <v>45316</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13280,7 +13280,7 @@
         <v>46069</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>44523</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         <v>44565</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>44783</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>44846</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>44802</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>44698</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>44529</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>44588</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         <v>44817</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14067,7 +14067,7 @@
         <v>44491</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14140,7 +14140,7 @@
         <v>44720</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>44502</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14291,7 +14291,7 @@
         <v>44746</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14364,7 +14364,7 @@
         <v>44859</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>44741</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>44495</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         <v>44529</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>44575</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         <v>45757</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>45099</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14880,7 +14880,7 @@
         <v>45626</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>45541</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
         <v>44900</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         <v>45743</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15182,7 +15182,7 @@
         <v>45104</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>45278</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>45583</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15406,7 +15406,7 @@
         <v>44817</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>45239</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15562,7 +15562,7 @@
         <v>45702</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>45610</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>45566</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15791,7 +15791,7 @@
         <v>45070</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>45350</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15937,7 +15937,7 @@
         <v>44501</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>45358</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16083,7 +16083,7 @@
         <v>44546</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16156,7 +16156,7 @@
         <v>45558</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16229,7 +16229,7 @@
         <v>45505</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>45459</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>45239</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16453,7 +16453,7 @@
         <v>45218</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>45287</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
         <v>44628</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>45534</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>45509</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>45230</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         <v>45163</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
         <v>45889</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>44914</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>45889</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17208,7 +17208,7 @@
         <v>45770</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17281,7 +17281,7 @@
         <v>45770</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>45895</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17432,7 +17432,7 @@
         <v>45623</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
         <v>45610</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>45615</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>45906</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17739,7 +17739,7 @@
         <v>44917</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17812,7 +17812,7 @@
         <v>45743</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>45474</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17963,7 +17963,7 @@
         <v>45407</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18041,7 +18041,7 @@
         <v>45429</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18114,7 +18114,7 @@
         <v>45278</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18187,7 +18187,7 @@
         <v>45538</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18260,7 +18260,7 @@
         <v>45187</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18338,7 +18338,7 @@
         <v>45337</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         <v>45111</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18489,7 +18489,7 @@
         <v>45170</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18562,7 +18562,7 @@
         <v>45617</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         <v>45541</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18718,7 +18718,7 @@
         <v>44532</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18791,7 +18791,7 @@
         <v>45278</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18864,7 +18864,7 @@
         <v>45342</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18937,7 +18937,7 @@
         <v>45590</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19010,7 +19010,7 @@
         <v>45603</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19083,7 +19083,7 @@
         <v>45055</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19161,7 +19161,7 @@
         <v>45022</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19239,7 +19239,7 @@
         <v>45541</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19317,7 +19317,7 @@
         <v>44956</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19395,7 +19395,7 @@
         <v>45573</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19473,7 +19473,7 @@
         <v>45573</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>45551</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19629,7 +19629,7 @@
         <v>45462</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19707,7 +19707,7 @@
         <v>44662</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>45230</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>45933</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>45350</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20004,7 +20004,7 @@
         <v>45799</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>45610</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20155,7 +20155,7 @@
         <v>45576</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20228,7 +20228,7 @@
         <v>45429</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20301,7 +20301,7 @@
         <v>45729</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20374,7 +20374,7 @@
         <v>45701</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20447,7 +20447,7 @@
         <v>45569</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>45818</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20598,7 +20598,7 @@
         <v>45818</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20676,7 +20676,7 @@
         <v>45254</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20749,7 +20749,7 @@
         <v>45701</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20822,7 +20822,7 @@
         <v>45175</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20895,7 +20895,7 @@
         <v>45827</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20968,7 +20968,7 @@
         <v>45951</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21041,7 +21041,7 @@
         <v>44509</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>45233</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>45951</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21260,7 +21260,7 @@
         <v>45953</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>45952</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21411,7 +21411,7 @@
         <v>45756</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21484,7 +21484,7 @@
         <v>45253</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21557,7 +21557,7 @@
         <v>45963</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>45792</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21708,7 +21708,7 @@
         <v>45784</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>44783</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>45840</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>45194</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>45840</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>45968</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>45933</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22234,7 +22234,7 @@
         <v>45061</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>45889</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22390,7 +22390,7 @@
         <v>45268</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22463,7 +22463,7 @@
         <v>45840</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22541,7 +22541,7 @@
         <v>44792</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22614,7 +22614,7 @@
         <v>45840</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22692,7 +22692,7 @@
         <v>45971</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22765,7 +22765,7 @@
         <v>44805</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>45316</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22916,7 +22916,7 @@
         <v>45848</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22989,7 +22989,7 @@
         <v>45268</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23062,7 +23062,7 @@
         <v>45973</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23140,7 +23140,7 @@
         <v>45743</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23218,7 +23218,7 @@
         <v>45757</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23291,7 +23291,7 @@
         <v>45866</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23369,7 +23369,7 @@
         <v>45866</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>45867</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>45975</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23588,7 +23588,7 @@
         <v>45708</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>45267</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23734,7 +23734,7 @@
         <v>45748</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23807,7 +23807,7 @@
         <v>44495</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23880,7 +23880,7 @@
         <v>45268</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>45729</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24026,7 +24026,7 @@
         <v>45784</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
         <v>46099</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24177,7 +24177,7 @@
         <v>45615</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>45216</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>46098</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24406,7 +24406,7 @@
         <v>46098</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24479,7 +24479,7 @@
         <v>46098</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24557,7 +24557,7 @@
         <v>46098</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>46098</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24708,7 +24708,7 @@
         <v>45296</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24781,7 +24781,7 @@
         <v>46099</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>45070</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24932,7 +24932,7 @@
         <v>45230</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25005,7 +25005,7 @@
         <v>46105</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25083,7 +25083,7 @@
         <v>46105</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
         <v>45474</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>45173</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25317,7 +25317,7 @@
         <v>45880</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>46108</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25468,7 +25468,7 @@
         <v>46111</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25541,7 +25541,7 @@
         <v>45880</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25619,7 +25619,7 @@
         <v>46111</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25692,7 +25692,7 @@
         <v>44574</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>46125</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25843,7 +25843,7 @@
         <v>46124</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25921,7 +25921,7 @@
         <v>46122</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25999,7 +25999,7 @@
         <v>46125</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26072,7 +26072,7 @@
         <v>44575</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26145,7 +26145,7 @@
         <v>46128</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26223,7 +26223,7 @@
         <v>46128</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26301,7 +26301,7 @@
         <v>44911</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26374,7 +26374,7 @@
         <v>44757</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26452,7 +26452,7 @@
         <v>46134</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>46132</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26608,7 +26608,7 @@
         <v>46134</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26681,7 +26681,7 @@
         <v>45905</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26759,7 +26759,7 @@
         <v>46007</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26832,7 +26832,7 @@
         <v>45172</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26910,7 +26910,7 @@
         <v>46136</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26988,7 +26988,7 @@
         <v>45113</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27066,7 +27066,7 @@
         <v>44909</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27139,7 +27139,7 @@
         <v>46020</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27212,7 +27212,7 @@
         <v>46020</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27285,7 +27285,7 @@
         <v>45940</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27363,7 +27363,7 @@
         <v>46021</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27436,7 +27436,7 @@
         <v>46083</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27509,7 +27509,7 @@
         <v>45230</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27582,7 +27582,7 @@
         <v>46030</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27655,7 +27655,7 @@
         <v>46056</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27728,7 +27728,7 @@
         <v>44750</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>46033</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>45895</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>46034</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28025,7 +28025,7 @@
         <v>45190</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28103,7 +28103,7 @@
         <v>46035</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28176,7 +28176,7 @@
         <v>45484</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28254,7 +28254,7 @@
         <v>45810</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         <v>45209</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28400,7 +28400,7 @@
         <v>45551</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28478,7 +28478,7 @@
         <v>46036</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28556,7 +28556,7 @@
         <v>45694</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28629,7 +28629,7 @@
         <v>46069</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>46034</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28775,7 +28775,7 @@
         <v>46037</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>45980</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28926,7 +28926,7 @@
         <v>46139</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29004,7 +29004,7 @@
         <v>46044</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29077,7 +29077,7 @@
         <v>44733</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29150,7 +29150,7 @@
         <v>46043</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>46032</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29296,7 +29296,7 @@
         <v>46020</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29369,7 +29369,7 @@
         <v>45230</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>46050</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29515,7 +29515,7 @@
         <v>46051</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29588,7 +29588,7 @@
         <v>46051</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29661,7 +29661,7 @@
         <v>46051</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29734,7 +29734,7 @@
         <v>45252</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29807,7 +29807,7 @@
         <v>45260</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29880,7 +29880,7 @@
         <v>46048</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29953,7 +29953,7 @@
         <v>46066</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>46072</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>45989</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30182,7 +30182,7 @@
         <v>45995</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30260,7 +30260,7 @@
         <v>46114</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30338,7 +30338,7 @@
         <v>45469</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>46084</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30484,7 +30484,7 @@
         <v>45630</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30557,7 +30557,7 @@
         <v>46090</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>46157</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30708,7 +30708,7 @@
         <v>46094</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30781,7 +30781,7 @@
         <v>46164</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30859,7 +30859,7 @@
         <v>46161</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30932,7 +30932,7 @@
         <v>46163</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31005,7 +31005,7 @@
         <v>46167</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31083,7 +31083,7 @@
         <v>46169</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>46169</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>46062</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31312,7 +31312,7 @@
         <v>46030</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31385,7 +31385,7 @@
         <v>46174</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31463,7 +31463,7 @@
         <v>46174</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31541,7 +31541,7 @@
         <v>46177</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31619,7 +31619,7 @@
         <v>46177</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31697,7 +31697,7 @@
         <v>46099</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31770,7 +31770,7 @@
         <v>46178</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>46114</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>45943</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31999,7 +31999,7 @@
         <v>45919</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32077,7 +32077,7 @@
         <v>46178</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>45920</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32233,7 +32233,7 @@
         <v>45940</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32311,7 +32311,7 @@
         <v>46033</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32384,7 +32384,7 @@
         <v>46136</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32462,7 +32462,7 @@
         <v>46136</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32540,7 +32540,7 @@
         <v>46136</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32618,7 +32618,7 @@
         <v>46183</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32696,7 +32696,7 @@
         <v>46185</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32774,7 +32774,7 @@
         <v>46148</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32852,7 +32852,7 @@
         <v>46198</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32930,7 +32930,7 @@
         <v>45086</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33008,7 +33008,7 @@
         <v>46212</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33086,7 +33086,7 @@
         <v>46266</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33164,7 +33164,7 @@
         <v>46266</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33242,7 +33242,7 @@
         <v>46225</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33320,7 +33320,7 @@
         <v>46273</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33398,7 +33398,7 @@
         <v>46167</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
         <v>46279</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33554,7 +33554,7 @@
         <v>46279</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33632,7 +33632,7 @@
         <v>46279</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33710,7 +33710,7 @@
         <v>46281</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33783,7 +33783,7 @@
         <v>46282</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>46281</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33934,7 +33934,7 @@
         <v>46281</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34012,7 +34012,7 @@
         <v>46239</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>46281</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>46281</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34246,7 +34246,7 @@
         <v>46240</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34319,7 +34319,7 @@
         <v>46240</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34392,7 +34392,7 @@
         <v>46281</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34470,7 +34470,7 @@
         <v>46286</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34543,7 +34543,7 @@
         <v>46281</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34621,7 +34621,7 @@
         <v>46058</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34694,7 +34694,7 @@
         <v>46244</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>46178</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>46290</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34923,7 +34923,7 @@
         <v>46174</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35001,7 +35001,7 @@
         <v>45958</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35079,7 +35079,7 @@
         <v>45958</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35157,7 +35157,7 @@
         <v>45957</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35230,7 +35230,7 @@
         <v>45086</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35308,7 +35308,7 @@
         <v>46296</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35386,7 +35386,7 @@
         <v>46072</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35459,7 +35459,7 @@
         <v>46072</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35532,7 +35532,7 @@
         <v>46255</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35610,7 +35610,7 @@
         <v>46300</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35683,7 +35683,7 @@
         <v>46300</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35756,7 +35756,7 @@
         <v>46255</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35834,7 +35834,7 @@
         <v>46300</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35907,7 +35907,7 @@
         <v>46255</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35985,7 +35985,7 @@
         <v>46301</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36058,7 +36058,7 @@
         <v>46262</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36131,7 +36131,7 @@
         <v>46212</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36209,7 +36209,7 @@
         <v>44102</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36287,7 +36287,7 @@
         <v>44550</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36365,7 +36365,7 @@
         <v>44671</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36443,7 +36443,7 @@
         <v>45700</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36521,7 +36521,7 @@
         <v>45700</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36599,7 +36599,7 @@
         <v>45317</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36677,7 +36677,7 @@
         <v>45316</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36755,7 +36755,7 @@
         <v>45720</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36833,7 +36833,7 @@
         <v>45706</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36911,7 +36911,7 @@
         <v>45906</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36989,7 +36989,7 @@
         <v>45989</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>45995</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37145,7 +37145,7 @@
         <v>46070</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>45700</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37301,7 +37301,7 @@
         <v>46142</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37379,7 +37379,7 @@
         <v>46125</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37457,7 +37457,7 @@
         <v>45971</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37530,7 +37530,7 @@
         <v>46085</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>

--- a/Översikt HEDEMORA.xlsx
+++ b/Översikt HEDEMORA.xlsx
@@ -601,7 +601,7 @@
         <v>45105</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>45996</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>44655</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>46197</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>45180</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>46033</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>45239</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>45628</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>45527</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>45527</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>46033</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>44502</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>45940</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>45616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>45919</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>46150</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>45527</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>46078</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>46020</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>46178</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>45961</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>45702</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>45527</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>45301</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>46251</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>45887</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>45469</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>45897</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>44489</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>46033</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>46055</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>46178</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>45702</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>46062</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>44588</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>46033</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>46198</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>46198</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>46239</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>44502</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>46048</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>46051</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>44579</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>45664</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>45933</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44961</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>45565</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>46051</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>44582</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>46239</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>44550</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>44523</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>45527</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>44883</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7078,7 +7078,7 @@
         <v>45642</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>45821</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>45825</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7423,7 +7423,7 @@
         <v>46000</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>45171</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         <v>44945</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>46146</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         <v>46070</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>46157</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>46177</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>46176</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>46178</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         <v>46178</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>46185</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>45670</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8760,7 +8760,7 @@
         <v>46240</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8871,7 +8871,7 @@
         <v>45001</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>44550</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>44585</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>45317</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>44880</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>44574</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>44864</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>44880</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>45757</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
         <v>45889</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>44918</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>45275</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>45743</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         <v>45226</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10423,7 +10423,7 @@
         <v>45842</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>45818</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         <v>45818</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10753,7 +10753,7 @@
         <v>44680</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>45610</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10972,7 +10972,7 @@
         <v>45743</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>45743</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11192,7 +11192,7 @@
         <v>45767</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>45763</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11407,7 +11407,7 @@
         <v>45615</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>46062</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         <v>45441</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>45008</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
         <v>46105</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         <v>46164</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>46177</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>45933</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>46204</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12389,7 +12389,7 @@
         <v>46212</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
         <v>46213</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12608,7 +12608,7 @@
         <v>46266</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
         <v>46245</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>46296</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12938,7 +12938,7 @@
         <v>44550</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>45319</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
         <v>45316</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13280,7 +13280,7 @@
         <v>46069</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>44523</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         <v>44565</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>44783</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>44846</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>44802</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>44698</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>44529</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>44588</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         <v>44817</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14067,7 +14067,7 @@
         <v>44491</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14140,7 +14140,7 @@
         <v>44720</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>44502</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14291,7 +14291,7 @@
         <v>44746</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14364,7 +14364,7 @@
         <v>44859</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>44741</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>44495</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         <v>44529</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>44575</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         <v>45757</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>45099</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14880,7 +14880,7 @@
         <v>45626</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>45541</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
         <v>44900</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         <v>45743</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15182,7 +15182,7 @@
         <v>45104</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>45278</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>45583</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15406,7 +15406,7 @@
         <v>44817</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>45239</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15562,7 +15562,7 @@
         <v>45702</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>45610</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>45566</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15791,7 +15791,7 @@
         <v>45070</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>45350</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15937,7 +15937,7 @@
         <v>44501</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>45358</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16083,7 +16083,7 @@
         <v>44546</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16156,7 +16156,7 @@
         <v>45558</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16229,7 +16229,7 @@
         <v>45505</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>45459</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>45239</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16453,7 +16453,7 @@
         <v>45218</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>45287</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
         <v>44628</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>45534</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>45509</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>45230</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         <v>45163</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
         <v>45889</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>44914</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>45889</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17208,7 +17208,7 @@
         <v>45770</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17281,7 +17281,7 @@
         <v>45770</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>45895</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17432,7 +17432,7 @@
         <v>45623</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
         <v>45610</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>45615</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>45906</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17739,7 +17739,7 @@
         <v>44917</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17812,7 +17812,7 @@
         <v>45743</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>45474</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17963,7 +17963,7 @@
         <v>45407</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18041,7 +18041,7 @@
         <v>45429</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18114,7 +18114,7 @@
         <v>45278</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18187,7 +18187,7 @@
         <v>45538</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18260,7 +18260,7 @@
         <v>45187</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18338,7 +18338,7 @@
         <v>45337</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         <v>45111</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18489,7 +18489,7 @@
         <v>45170</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18562,7 +18562,7 @@
         <v>45617</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         <v>45541</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18718,7 +18718,7 @@
         <v>44532</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18791,7 +18791,7 @@
         <v>45278</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18864,7 +18864,7 @@
         <v>45342</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18937,7 +18937,7 @@
         <v>45590</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19010,7 +19010,7 @@
         <v>45603</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19083,7 +19083,7 @@
         <v>45055</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19161,7 +19161,7 @@
         <v>45022</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19239,7 +19239,7 @@
         <v>45541</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19317,7 +19317,7 @@
         <v>44956</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19395,7 +19395,7 @@
         <v>45573</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19473,7 +19473,7 @@
         <v>45573</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>45551</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19629,7 +19629,7 @@
         <v>45462</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19707,7 +19707,7 @@
         <v>44662</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>45230</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>45933</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>45350</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20004,7 +20004,7 @@
         <v>45799</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>45610</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20155,7 +20155,7 @@
         <v>45576</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20228,7 +20228,7 @@
         <v>45429</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20301,7 +20301,7 @@
         <v>45729</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20374,7 +20374,7 @@
         <v>45701</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20447,7 +20447,7 @@
         <v>45569</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>45818</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20598,7 +20598,7 @@
         <v>45818</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20676,7 +20676,7 @@
         <v>45254</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20749,7 +20749,7 @@
         <v>45701</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20822,7 +20822,7 @@
         <v>45175</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20895,7 +20895,7 @@
         <v>45827</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20968,7 +20968,7 @@
         <v>45951</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21041,7 +21041,7 @@
         <v>44509</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>45233</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>45951</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21260,7 +21260,7 @@
         <v>45953</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>45952</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21411,7 +21411,7 @@
         <v>45756</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21484,7 +21484,7 @@
         <v>45253</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21557,7 +21557,7 @@
         <v>45963</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>45792</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21708,7 +21708,7 @@
         <v>45784</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>44783</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>45840</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>45194</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>45840</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>45968</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>45933</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22234,7 +22234,7 @@
         <v>45061</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>45889</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22390,7 +22390,7 @@
         <v>45268</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22463,7 +22463,7 @@
         <v>45840</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22541,7 +22541,7 @@
         <v>44792</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22614,7 +22614,7 @@
         <v>45840</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22692,7 +22692,7 @@
         <v>45971</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22765,7 +22765,7 @@
         <v>44805</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>45316</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22916,7 +22916,7 @@
         <v>45848</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22989,7 +22989,7 @@
         <v>45268</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23062,7 +23062,7 @@
         <v>45973</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23140,7 +23140,7 @@
         <v>45743</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23218,7 +23218,7 @@
         <v>45757</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23291,7 +23291,7 @@
         <v>45866</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23369,7 +23369,7 @@
         <v>45866</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>45867</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>45975</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23588,7 +23588,7 @@
         <v>45708</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>45267</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23734,7 +23734,7 @@
         <v>45748</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23807,7 +23807,7 @@
         <v>44495</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23880,7 +23880,7 @@
         <v>45268</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>45729</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24026,7 +24026,7 @@
         <v>45784</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
         <v>46099</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24177,7 +24177,7 @@
         <v>45615</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>45216</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>46098</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24406,7 +24406,7 @@
         <v>46098</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24479,7 +24479,7 @@
         <v>46098</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24557,7 +24557,7 @@
         <v>46098</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>46098</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24708,7 +24708,7 @@
         <v>45296</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24781,7 +24781,7 @@
         <v>46099</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>45070</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24932,7 +24932,7 @@
         <v>45230</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25005,7 +25005,7 @@
         <v>46105</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25083,7 +25083,7 @@
         <v>46105</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
         <v>45474</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>45173</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25317,7 +25317,7 @@
         <v>45880</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>46108</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25468,7 +25468,7 @@
         <v>46111</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25541,7 +25541,7 @@
         <v>45880</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25619,7 +25619,7 @@
         <v>46111</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25692,7 +25692,7 @@
         <v>44574</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>46125</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25843,7 +25843,7 @@
         <v>46124</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25921,7 +25921,7 @@
         <v>46122</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25999,7 +25999,7 @@
         <v>46125</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26072,7 +26072,7 @@
         <v>44575</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26145,7 +26145,7 @@
         <v>46128</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26223,7 +26223,7 @@
         <v>46128</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26301,7 +26301,7 @@
         <v>44911</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26374,7 +26374,7 @@
         <v>44757</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26452,7 +26452,7 @@
         <v>46134</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>46132</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26608,7 +26608,7 @@
         <v>46134</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26681,7 +26681,7 @@
         <v>45905</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26759,7 +26759,7 @@
         <v>46007</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26832,7 +26832,7 @@
         <v>45172</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26910,7 +26910,7 @@
         <v>46136</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26988,7 +26988,7 @@
         <v>45113</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27066,7 +27066,7 @@
         <v>44909</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27139,7 +27139,7 @@
         <v>46020</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27212,7 +27212,7 @@
         <v>46020</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27285,7 +27285,7 @@
         <v>45940</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27363,7 +27363,7 @@
         <v>46021</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27436,7 +27436,7 @@
         <v>46083</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27509,7 +27509,7 @@
         <v>45230</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27582,7 +27582,7 @@
         <v>46030</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27655,7 +27655,7 @@
         <v>46056</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27728,7 +27728,7 @@
         <v>44750</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>46033</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>45895</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>46034</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28025,7 +28025,7 @@
         <v>45190</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28103,7 +28103,7 @@
         <v>46035</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28176,7 +28176,7 @@
         <v>45484</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28254,7 +28254,7 @@
         <v>45810</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         <v>45209</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28400,7 +28400,7 @@
         <v>45551</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28478,7 +28478,7 @@
         <v>46036</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28556,7 +28556,7 @@
         <v>45694</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28629,7 +28629,7 @@
         <v>46069</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>46034</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28775,7 +28775,7 @@
         <v>46037</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>45980</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28926,7 +28926,7 @@
         <v>46139</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29004,7 +29004,7 @@
         <v>46044</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29077,7 +29077,7 @@
         <v>44733</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29150,7 +29150,7 @@
         <v>46043</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>46032</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29296,7 +29296,7 @@
         <v>46020</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29369,7 +29369,7 @@
         <v>45230</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>46050</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29515,7 +29515,7 @@
         <v>46051</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29588,7 +29588,7 @@
         <v>46051</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29661,7 +29661,7 @@
         <v>46051</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29734,7 +29734,7 @@
         <v>45252</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29807,7 +29807,7 @@
         <v>45260</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29880,7 +29880,7 @@
         <v>46048</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29953,7 +29953,7 @@
         <v>46066</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>46072</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>45989</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30182,7 +30182,7 @@
         <v>45995</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30260,7 +30260,7 @@
         <v>46114</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30338,7 +30338,7 @@
         <v>45469</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>46084</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30484,7 +30484,7 @@
         <v>45630</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30557,7 +30557,7 @@
         <v>46090</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>46157</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30708,7 +30708,7 @@
         <v>46094</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30781,7 +30781,7 @@
         <v>46164</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30859,7 +30859,7 @@
         <v>46161</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30932,7 +30932,7 @@
         <v>46163</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31005,7 +31005,7 @@
         <v>46167</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31083,7 +31083,7 @@
         <v>46169</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>46169</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>46062</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31312,7 +31312,7 @@
         <v>46030</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31385,7 +31385,7 @@
         <v>46174</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31463,7 +31463,7 @@
         <v>46174</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31541,7 +31541,7 @@
         <v>46177</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31619,7 +31619,7 @@
         <v>46177</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31697,7 +31697,7 @@
         <v>46099</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31770,7 +31770,7 @@
         <v>46178</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>46114</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>45943</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31999,7 +31999,7 @@
         <v>45919</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32077,7 +32077,7 @@
         <v>46178</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>45920</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32233,7 +32233,7 @@
         <v>45940</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32311,7 +32311,7 @@
         <v>46033</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32384,7 +32384,7 @@
         <v>46136</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32462,7 +32462,7 @@
         <v>46136</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32540,7 +32540,7 @@
         <v>46136</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32618,7 +32618,7 @@
         <v>46183</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32696,7 +32696,7 @@
         <v>46185</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32774,7 +32774,7 @@
         <v>46148</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32852,7 +32852,7 @@
         <v>46198</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32930,7 +32930,7 @@
         <v>45086</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33008,7 +33008,7 @@
         <v>46212</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33086,7 +33086,7 @@
         <v>46266</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33164,7 +33164,7 @@
         <v>46266</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33242,7 +33242,7 @@
         <v>46225</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33320,7 +33320,7 @@
         <v>46273</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33398,7 +33398,7 @@
         <v>46167</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
         <v>46279</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33554,7 +33554,7 @@
         <v>46279</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33632,7 +33632,7 @@
         <v>46279</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33710,7 +33710,7 @@
         <v>46281</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33783,7 +33783,7 @@
         <v>46282</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>46281</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33934,7 +33934,7 @@
         <v>46281</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34012,7 +34012,7 @@
         <v>46239</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>46281</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>46281</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34246,7 +34246,7 @@
         <v>46240</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34319,7 +34319,7 @@
         <v>46240</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34392,7 +34392,7 @@
         <v>46281</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34470,7 +34470,7 @@
         <v>46286</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34543,7 +34543,7 @@
         <v>46281</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34621,7 +34621,7 @@
         <v>46058</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34694,7 +34694,7 @@
         <v>46244</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>46178</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>46290</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34923,7 +34923,7 @@
         <v>46174</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35001,7 +35001,7 @@
         <v>45958</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35079,7 +35079,7 @@
         <v>45958</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35157,7 +35157,7 @@
         <v>45957</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35230,7 +35230,7 @@
         <v>45086</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35308,7 +35308,7 @@
         <v>46296</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35386,7 +35386,7 @@
         <v>46072</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35459,7 +35459,7 @@
         <v>46072</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35532,7 +35532,7 @@
         <v>46255</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35610,7 +35610,7 @@
         <v>46300</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35683,7 +35683,7 @@
         <v>46300</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35756,7 +35756,7 @@
         <v>46255</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35834,7 +35834,7 @@
         <v>46300</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35907,7 +35907,7 @@
         <v>46255</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35985,7 +35985,7 @@
         <v>46301</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36058,7 +36058,7 @@
         <v>46262</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36131,7 +36131,7 @@
         <v>46212</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36209,7 +36209,7 @@
         <v>44102</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36287,7 +36287,7 @@
         <v>44550</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36365,7 +36365,7 @@
         <v>44671</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36443,7 +36443,7 @@
         <v>45700</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36521,7 +36521,7 @@
         <v>45700</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36599,7 +36599,7 @@
         <v>45317</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36677,7 +36677,7 @@
         <v>45316</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36755,7 +36755,7 @@
         <v>45720</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36833,7 +36833,7 @@
         <v>45706</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36911,7 +36911,7 @@
         <v>45906</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36989,7 +36989,7 @@
         <v>45989</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>45995</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37145,7 +37145,7 @@
         <v>46070</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>45700</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37301,7 +37301,7 @@
         <v>46142</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37379,7 +37379,7 @@
         <v>46125</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37457,7 +37457,7 @@
         <v>45971</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37530,7 +37530,7 @@
         <v>46085</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>

--- a/Översikt HEDEMORA.xlsx
+++ b/Översikt HEDEMORA.xlsx
@@ -601,7 +601,7 @@
         <v>45105</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>45996</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>44655</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>46197</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>45180</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>46033</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>45239</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>45628</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>45527</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>46033</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>44502</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>45527</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>45940</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>45616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>45919</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>46150</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>45527</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>46078</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>46020</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>46178</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>45961</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>45702</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>45301</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         <v>45527</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>46251</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>45887</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>45469</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>45897</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>46055</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>44489</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>46178</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>46033</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>45702</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>46062</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>44588</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>46033</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>46198</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>46198</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>46239</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>46051</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>44502</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>46048</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>45565</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>45664</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>45933</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>46051</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>44579</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>44582</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>44961</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>46239</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>44550</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>44523</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>44883</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>45642</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
         <v>45527</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>46146</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         <v>46157</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>45171</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
         <v>46000</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         <v>46176</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         <v>46177</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>46178</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>46178</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>44945</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         <v>46070</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>46185</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         <v>46240</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>45670</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
         <v>45821</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>45825</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8871,7 +8871,7 @@
         <v>45001</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>44550</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>44585</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>45317</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>44880</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>44574</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>44880</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>44864</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>45889</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>45743</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
         <v>46105</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>45842</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>46164</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>45933</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>46177</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>45008</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10649,7 +10649,7 @@
         <v>45441</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>46062</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>45275</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10972,7 +10972,7 @@
         <v>45610</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>45763</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>46204</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>44918</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         <v>45226</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11519,7 +11519,7 @@
         <v>45615</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>44680</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
         <v>45757</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11839,7 +11839,7 @@
         <v>46212</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>46213</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12058,7 +12058,7 @@
         <v>46245</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>46296</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>46300</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>46300</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>46266</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>45818</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>45818</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>45743</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12932,7 +12932,7 @@
         <v>45743</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13042,7 +13042,7 @@
         <v>45767</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         <v>45319</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13270,7 +13270,7 @@
         <v>45316</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>44550</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>46069</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
         <v>44523</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>44565</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>44783</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>44846</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>44802</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>44698</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14052,7 +14052,7 @@
         <v>44529</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>44588</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14203,7 +14203,7 @@
         <v>44817</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>44491</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>44741</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14427,7 +14427,7 @@
         <v>44720</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14500,7 +14500,7 @@
         <v>44502</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14578,7 +14578,7 @@
         <v>44746</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         <v>44859</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>44495</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>44575</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14875,7 +14875,7 @@
         <v>45170</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14948,7 +14948,7 @@
         <v>45022</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>45459</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15099,7 +15099,7 @@
         <v>44628</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15177,7 +15177,7 @@
         <v>45175</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>44900</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15323,7 +15323,7 @@
         <v>44532</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15396,7 +15396,7 @@
         <v>45541</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15474,7 +15474,7 @@
         <v>45558</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>45342</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15620,7 +15620,7 @@
         <v>44956</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>44805</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>45407</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
         <v>45070</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>45610</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>45694</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         <v>45429</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>45218</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
         <v>45230</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>45230</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>45708</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16443,7 +16443,7 @@
         <v>45099</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>45216</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>44501</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16662,7 +16662,7 @@
         <v>44757</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16740,7 +16740,7 @@
         <v>45230</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16813,7 +16813,7 @@
         <v>45350</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>46136</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>45484</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17042,7 +17042,7 @@
         <v>45209</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>46056</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>46069</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>44792</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>46020</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17407,7 +17407,7 @@
         <v>44750</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>45895</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>45889</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17636,7 +17636,7 @@
         <v>45889</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>45810</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>45895</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17865,7 +17865,7 @@
         <v>45770</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         <v>45770</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>45534</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18089,7 +18089,7 @@
         <v>45551</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>46083</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>45253</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>45316</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>46034</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>45906</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18537,7 +18537,7 @@
         <v>45230</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18610,7 +18610,7 @@
         <v>45933</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18683,7 +18683,7 @@
         <v>45287</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18756,7 +18756,7 @@
         <v>45623</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>44914</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         <v>45951</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18975,7 +18975,7 @@
         <v>45951</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19048,7 +19048,7 @@
         <v>45469</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19121,7 +19121,7 @@
         <v>45953</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19199,7 +19199,7 @@
         <v>45952</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19272,7 +19272,7 @@
         <v>45566</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19350,7 +19350,7 @@
         <v>45505</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>46157</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>45538</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19574,7 +19574,7 @@
         <v>46114</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19652,7 +19652,7 @@
         <v>45630</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19725,7 +19725,7 @@
         <v>45963</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>44783</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19871,7 +19871,7 @@
         <v>45840</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19949,7 +19949,7 @@
         <v>45792</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         <v>45784</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>45729</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>45933</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20251,7 +20251,7 @@
         <v>45968</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20324,7 +20324,7 @@
         <v>45840</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20402,7 +20402,7 @@
         <v>45889</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20480,7 +20480,7 @@
         <v>46161</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20553,7 +20553,7 @@
         <v>45971</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         <v>45973</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20704,7 +20704,7 @@
         <v>45626</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20782,7 +20782,7 @@
         <v>45975</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20855,7 +20855,7 @@
         <v>45743</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20928,7 +20928,7 @@
         <v>45729</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21001,7 +21001,7 @@
         <v>46163</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21074,7 +21074,7 @@
         <v>45583</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>45576</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21220,7 +21220,7 @@
         <v>46164</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         <v>46167</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
         <v>45172</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>45880</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>45880</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>45190</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21688,7 +21688,7 @@
         <v>46169</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21766,7 +21766,7 @@
         <v>44662</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21844,7 +21844,7 @@
         <v>45061</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>46169</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22000,7 +22000,7 @@
         <v>45702</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
         <v>45230</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>45610</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
         <v>46007</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>46174</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>45756</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22448,7 +22448,7 @@
         <v>45905</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>44817</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22604,7 +22604,7 @@
         <v>46174</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22682,7 +22682,7 @@
         <v>45278</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22755,7 +22755,7 @@
         <v>45233</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>45268</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22901,7 +22901,7 @@
         <v>45268</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>45070</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23047,7 +23047,7 @@
         <v>46062</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         <v>46020</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23193,7 +23193,7 @@
         <v>46021</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23266,7 +23266,7 @@
         <v>46020</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23339,7 +23339,7 @@
         <v>45940</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23417,7 +23417,7 @@
         <v>46030</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23490,7 +23490,7 @@
         <v>46035</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23563,7 +23563,7 @@
         <v>46033</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23636,7 +23636,7 @@
         <v>46030</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
         <v>46034</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23782,7 +23782,7 @@
         <v>46036</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23860,7 +23860,7 @@
         <v>46177</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23938,7 +23938,7 @@
         <v>46177</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24016,7 +24016,7 @@
         <v>46178</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24094,7 +24094,7 @@
         <v>46136</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24172,7 +24172,7 @@
         <v>46037</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24245,7 +24245,7 @@
         <v>46099</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
         <v>46114</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24396,7 +24396,7 @@
         <v>46136</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24474,7 +24474,7 @@
         <v>45980</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24552,7 +24552,7 @@
         <v>45940</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>45920</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24708,7 +24708,7 @@
         <v>46136</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24786,7 +24786,7 @@
         <v>46043</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>45615</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24937,7 +24937,7 @@
         <v>46178</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25015,7 +25015,7 @@
         <v>46033</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>45919</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25166,7 +25166,7 @@
         <v>46032</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>45943</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>46044</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25385,7 +25385,7 @@
         <v>46051</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>46051</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25531,7 +25531,7 @@
         <v>46050</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25604,7 +25604,7 @@
         <v>46051</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25677,7 +25677,7 @@
         <v>45474</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25755,7 +25755,7 @@
         <v>45252</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>45260</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25901,7 +25901,7 @@
         <v>46048</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25974,7 +25974,7 @@
         <v>45474</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26052,7 +26052,7 @@
         <v>46183</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>46148</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26208,7 +26208,7 @@
         <v>46066</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>46072</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26359,7 +26359,7 @@
         <v>45989</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26437,7 +26437,7 @@
         <v>45617</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>45995</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>46185</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26671,7 +26671,7 @@
         <v>45610</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26749,7 +26749,7 @@
         <v>45254</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26822,7 +26822,7 @@
         <v>46084</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26895,7 +26895,7 @@
         <v>45541</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         <v>46090</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>45350</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27119,7 +27119,7 @@
         <v>44546</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         <v>46094</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27265,7 +27265,7 @@
         <v>46098</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27343,7 +27343,7 @@
         <v>46098</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27421,7 +27421,7 @@
         <v>46098</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
         <v>46098</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27572,7 +27572,7 @@
         <v>46098</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27645,7 +27645,7 @@
         <v>46099</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27718,7 +27718,7 @@
         <v>46099</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27796,7 +27796,7 @@
         <v>45104</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27874,7 +27874,7 @@
         <v>46105</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>46105</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28030,7 +28030,7 @@
         <v>46108</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28103,7 +28103,7 @@
         <v>44917</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28176,7 +28176,7 @@
         <v>46111</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28249,7 +28249,7 @@
         <v>46198</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         <v>46111</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28400,7 +28400,7 @@
         <v>46122</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28478,7 +28478,7 @@
         <v>45267</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>46124</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28629,7 +28629,7 @@
         <v>46125</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>46125</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28775,7 +28775,7 @@
         <v>46128</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>44574</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28931,7 +28931,7 @@
         <v>45509</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29004,7 +29004,7 @@
         <v>46128</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29082,7 +29082,7 @@
         <v>46132</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29160,7 +29160,7 @@
         <v>45743</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29233,7 +29233,7 @@
         <v>45296</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29306,7 +29306,7 @@
         <v>45163</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>46134</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29462,7 +29462,7 @@
         <v>46134</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29535,7 +29535,7 @@
         <v>45239</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29613,7 +29613,7 @@
         <v>45748</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29686,7 +29686,7 @@
         <v>46139</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29764,7 +29764,7 @@
         <v>45615</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29842,7 +29842,7 @@
         <v>45573</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29920,7 +29920,7 @@
         <v>45573</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29998,7 +29998,7 @@
         <v>45551</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30076,7 +30076,7 @@
         <v>44575</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30149,7 +30149,7 @@
         <v>46212</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30227,7 +30227,7 @@
         <v>45757</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30300,7 +30300,7 @@
         <v>45086</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30378,7 +30378,7 @@
         <v>44733</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30451,7 +30451,7 @@
         <v>44911</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30524,7 +30524,7 @@
         <v>45278</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30597,7 +30597,7 @@
         <v>46225</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>44495</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30748,7 +30748,7 @@
         <v>46273</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30826,7 +30826,7 @@
         <v>45268</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30899,7 +30899,7 @@
         <v>46279</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30977,7 +30977,7 @@
         <v>46279</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>44509</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31128,7 +31128,7 @@
         <v>46167</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>46279</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31284,7 +31284,7 @@
         <v>45358</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31357,7 +31357,7 @@
         <v>45239</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31435,7 +31435,7 @@
         <v>46281</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31513,7 +31513,7 @@
         <v>46281</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31591,7 +31591,7 @@
         <v>46281</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31669,7 +31669,7 @@
         <v>46281</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31747,7 +31747,7 @@
         <v>46281</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31820,7 +31820,7 @@
         <v>46240</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31893,7 +31893,7 @@
         <v>46240</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31966,7 +31966,7 @@
         <v>45757</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32039,7 +32039,7 @@
         <v>46281</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32117,7 +32117,7 @@
         <v>46282</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32190,7 +32190,7 @@
         <v>46239</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32268,7 +32268,7 @@
         <v>46281</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>45541</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32424,7 +32424,7 @@
         <v>46286</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32497,7 +32497,7 @@
         <v>46244</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32570,7 +32570,7 @@
         <v>46058</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32643,7 +32643,7 @@
         <v>46178</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32721,7 +32721,7 @@
         <v>45701</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32794,7 +32794,7 @@
         <v>45957</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32867,7 +32867,7 @@
         <v>45958</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32945,7 +32945,7 @@
         <v>45958</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33023,7 +33023,7 @@
         <v>46290</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33101,7 +33101,7 @@
         <v>44909</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>45086</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33252,7 +33252,7 @@
         <v>46174</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33330,7 +33330,7 @@
         <v>45194</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33403,7 +33403,7 @@
         <v>45173</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33481,7 +33481,7 @@
         <v>45055</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33559,7 +33559,7 @@
         <v>44529</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33632,7 +33632,7 @@
         <v>45113</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33710,7 +33710,7 @@
         <v>46296</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33788,7 +33788,7 @@
         <v>46072</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33861,7 +33861,7 @@
         <v>46072</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33934,7 +33934,7 @@
         <v>45111</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34012,7 +34012,7 @@
         <v>45278</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34085,7 +34085,7 @@
         <v>45590</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34158,7 +34158,7 @@
         <v>45187</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34236,7 +34236,7 @@
         <v>46301</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34309,7 +34309,7 @@
         <v>46300</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34382,7 +34382,7 @@
         <v>45337</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34455,7 +34455,7 @@
         <v>46255</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34533,7 +34533,7 @@
         <v>46255</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34611,7 +34611,7 @@
         <v>45603</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34684,7 +34684,7 @@
         <v>46255</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34762,7 +34762,7 @@
         <v>46212</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34840,7 +34840,7 @@
         <v>45462</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34918,7 +34918,7 @@
         <v>45799</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34991,7 +34991,7 @@
         <v>46262</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35064,7 +35064,7 @@
         <v>45429</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35137,7 +35137,7 @@
         <v>46266</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35215,7 +35215,7 @@
         <v>46266</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35293,7 +35293,7 @@
         <v>45569</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35366,7 +35366,7 @@
         <v>45701</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35439,7 +35439,7 @@
         <v>45818</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35517,7 +35517,7 @@
         <v>45818</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35595,7 +35595,7 @@
         <v>45827</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35668,7 +35668,7 @@
         <v>45840</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35746,7 +35746,7 @@
         <v>45840</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35824,7 +35824,7 @@
         <v>45848</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>45743</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35975,7 +35975,7 @@
         <v>45866</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36048,7 +36048,7 @@
         <v>45866</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36126,7 +36126,7 @@
         <v>45867</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36199,7 +36199,7 @@
         <v>45784</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36277,7 +36277,7 @@
         <v>44102</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36355,7 +36355,7 @@
         <v>45700</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>45700</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36511,7 +36511,7 @@
         <v>44550</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36589,7 +36589,7 @@
         <v>45317</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36667,7 +36667,7 @@
         <v>45316</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36745,7 +36745,7 @@
         <v>44671</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36823,7 +36823,7 @@
         <v>45720</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36901,7 +36901,7 @@
         <v>45706</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36979,7 +36979,7 @@
         <v>45906</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37057,7 +37057,7 @@
         <v>45989</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37135,7 +37135,7 @@
         <v>45995</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37213,7 +37213,7 @@
         <v>46070</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37291,7 +37291,7 @@
         <v>45700</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37369,7 +37369,7 @@
         <v>46142</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37447,7 +37447,7 @@
         <v>46125</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37525,7 +37525,7 @@
         <v>45971</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37598,7 +37598,7 @@
         <v>46085</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>

--- a/Översikt HEDEMORA.xlsx
+++ b/Översikt HEDEMORA.xlsx
@@ -601,7 +601,7 @@
         <v>45105</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>45996</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>44655</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>46197</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>45180</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>46033</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>45239</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>45628</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>45527</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>46033</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>44502</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>45527</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>45940</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>45616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>45919</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>46150</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>45527</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>46078</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>46020</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>46178</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>45961</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>45702</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>45301</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         <v>45527</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>46251</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>45887</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>45469</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>45897</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>46055</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>44489</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>46178</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>46033</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>45702</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>46062</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>44588</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>46033</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>46198</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>46198</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>46239</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>46051</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>44502</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>46048</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>45565</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>45664</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>45933</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>46051</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>44579</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>44582</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>44961</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>46239</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>44550</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>44523</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>44883</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>45642</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
         <v>45527</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>46146</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         <v>46157</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>45171</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
         <v>46000</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         <v>46176</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         <v>46177</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>46178</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>46178</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>44945</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         <v>46070</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>46185</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         <v>46240</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>45670</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
         <v>45821</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>45825</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8871,7 +8871,7 @@
         <v>45001</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>44550</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>44585</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>45317</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>44880</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>44574</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>44880</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>44864</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>45889</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>45743</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
         <v>46105</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>45842</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>46164</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>45933</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>46177</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>45008</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10649,7 +10649,7 @@
         <v>45441</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>46062</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>45275</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10972,7 +10972,7 @@
         <v>45610</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>45763</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>46204</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>44918</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         <v>45226</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11519,7 +11519,7 @@
         <v>45615</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>44680</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
         <v>45757</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11839,7 +11839,7 @@
         <v>46212</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>46213</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12058,7 +12058,7 @@
         <v>46245</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>46296</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>46300</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>46300</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>46266</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>45818</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>45818</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>45743</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12932,7 +12932,7 @@
         <v>45743</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13042,7 +13042,7 @@
         <v>45767</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         <v>45319</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13270,7 +13270,7 @@
         <v>45316</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>44550</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>46069</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
         <v>44523</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>44565</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>44783</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>44846</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>44802</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>44698</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14052,7 +14052,7 @@
         <v>44529</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>44588</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14203,7 +14203,7 @@
         <v>44817</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>44491</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>44741</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14427,7 +14427,7 @@
         <v>44720</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14500,7 +14500,7 @@
         <v>44502</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14578,7 +14578,7 @@
         <v>44746</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         <v>44859</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>44495</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>44575</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14875,7 +14875,7 @@
         <v>45170</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14948,7 +14948,7 @@
         <v>45022</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>45459</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15099,7 +15099,7 @@
         <v>44628</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15177,7 +15177,7 @@
         <v>45175</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>44900</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15323,7 +15323,7 @@
         <v>44532</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15396,7 +15396,7 @@
         <v>45541</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15474,7 +15474,7 @@
         <v>45558</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>45342</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15620,7 +15620,7 @@
         <v>44956</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>44805</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>45407</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
         <v>45070</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>45610</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>45694</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         <v>45429</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>45218</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
         <v>45230</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>45230</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>45708</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16443,7 +16443,7 @@
         <v>45099</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>45216</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>44501</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16662,7 +16662,7 @@
         <v>44757</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16740,7 +16740,7 @@
         <v>45230</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16813,7 +16813,7 @@
         <v>45350</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>46136</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>45484</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17042,7 +17042,7 @@
         <v>45209</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>46056</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>46069</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>44792</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>46020</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17407,7 +17407,7 @@
         <v>44750</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>45895</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>45889</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17636,7 +17636,7 @@
         <v>45889</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>45810</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>45895</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17865,7 +17865,7 @@
         <v>45770</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         <v>45770</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>45534</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18089,7 +18089,7 @@
         <v>45551</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>46083</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>45253</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>45316</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>46034</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>45906</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18537,7 +18537,7 @@
         <v>45230</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18610,7 +18610,7 @@
         <v>45933</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18683,7 +18683,7 @@
         <v>45287</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18756,7 +18756,7 @@
         <v>45623</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>44914</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         <v>45951</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18975,7 +18975,7 @@
         <v>45951</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19048,7 +19048,7 @@
         <v>45469</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19121,7 +19121,7 @@
         <v>45953</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19199,7 +19199,7 @@
         <v>45952</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19272,7 +19272,7 @@
         <v>45566</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19350,7 +19350,7 @@
         <v>45505</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>46157</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>45538</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19574,7 +19574,7 @@
         <v>46114</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19652,7 +19652,7 @@
         <v>45630</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19725,7 +19725,7 @@
         <v>45963</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>44783</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19871,7 +19871,7 @@
         <v>45840</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19949,7 +19949,7 @@
         <v>45792</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         <v>45784</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>45729</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>45933</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20251,7 +20251,7 @@
         <v>45968</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20324,7 +20324,7 @@
         <v>45840</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20402,7 +20402,7 @@
         <v>45889</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20480,7 +20480,7 @@
         <v>46161</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20553,7 +20553,7 @@
         <v>45971</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         <v>45973</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20704,7 +20704,7 @@
         <v>45626</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20782,7 +20782,7 @@
         <v>45975</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20855,7 +20855,7 @@
         <v>45743</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20928,7 +20928,7 @@
         <v>45729</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21001,7 +21001,7 @@
         <v>46163</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21074,7 +21074,7 @@
         <v>45583</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>45576</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21220,7 +21220,7 @@
         <v>46164</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         <v>46167</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
         <v>45172</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>45880</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>45880</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>45190</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21688,7 +21688,7 @@
         <v>46169</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21766,7 +21766,7 @@
         <v>44662</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21844,7 +21844,7 @@
         <v>45061</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>46169</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22000,7 +22000,7 @@
         <v>45702</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
         <v>45230</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>45610</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
         <v>46007</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>46174</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>45756</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22448,7 +22448,7 @@
         <v>45905</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>44817</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22604,7 +22604,7 @@
         <v>46174</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22682,7 +22682,7 @@
         <v>45278</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22755,7 +22755,7 @@
         <v>45233</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>45268</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22901,7 +22901,7 @@
         <v>45268</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>45070</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23047,7 +23047,7 @@
         <v>46062</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         <v>46020</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23193,7 +23193,7 @@
         <v>46021</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23266,7 +23266,7 @@
         <v>46020</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23339,7 +23339,7 @@
         <v>45940</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23417,7 +23417,7 @@
         <v>46030</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23490,7 +23490,7 @@
         <v>46035</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23563,7 +23563,7 @@
         <v>46033</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23636,7 +23636,7 @@
         <v>46030</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
         <v>46034</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23782,7 +23782,7 @@
         <v>46036</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23860,7 +23860,7 @@
         <v>46177</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23938,7 +23938,7 @@
         <v>46177</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24016,7 +24016,7 @@
         <v>46178</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24094,7 +24094,7 @@
         <v>46136</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24172,7 +24172,7 @@
         <v>46037</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24245,7 +24245,7 @@
         <v>46099</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
         <v>46114</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24396,7 +24396,7 @@
         <v>46136</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24474,7 +24474,7 @@
         <v>45980</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24552,7 +24552,7 @@
         <v>45940</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>45920</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24708,7 +24708,7 @@
         <v>46136</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24786,7 +24786,7 @@
         <v>46043</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>45615</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24937,7 +24937,7 @@
         <v>46178</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25015,7 +25015,7 @@
         <v>46033</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>45919</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25166,7 +25166,7 @@
         <v>46032</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>45943</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>46044</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25385,7 +25385,7 @@
         <v>46051</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>46051</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25531,7 +25531,7 @@
         <v>46050</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25604,7 +25604,7 @@
         <v>46051</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25677,7 +25677,7 @@
         <v>45474</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25755,7 +25755,7 @@
         <v>45252</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>45260</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25901,7 +25901,7 @@
         <v>46048</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25974,7 +25974,7 @@
         <v>45474</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26052,7 +26052,7 @@
         <v>46183</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>46148</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26208,7 +26208,7 @@
         <v>46066</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>46072</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26359,7 +26359,7 @@
         <v>45989</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26437,7 +26437,7 @@
         <v>45617</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>45995</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>46185</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26671,7 +26671,7 @@
         <v>45610</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26749,7 +26749,7 @@
         <v>45254</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26822,7 +26822,7 @@
         <v>46084</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26895,7 +26895,7 @@
         <v>45541</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         <v>46090</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>45350</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27119,7 +27119,7 @@
         <v>44546</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         <v>46094</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27265,7 +27265,7 @@
         <v>46098</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27343,7 +27343,7 @@
         <v>46098</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27421,7 +27421,7 @@
         <v>46098</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
         <v>46098</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27572,7 +27572,7 @@
         <v>46098</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27645,7 +27645,7 @@
         <v>46099</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27718,7 +27718,7 @@
         <v>46099</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27796,7 +27796,7 @@
         <v>45104</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27874,7 +27874,7 @@
         <v>46105</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>46105</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28030,7 +28030,7 @@
         <v>46108</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28103,7 +28103,7 @@
         <v>44917</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28176,7 +28176,7 @@
         <v>46111</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28249,7 +28249,7 @@
         <v>46198</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         <v>46111</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28400,7 +28400,7 @@
         <v>46122</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28478,7 +28478,7 @@
         <v>45267</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>46124</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28629,7 +28629,7 @@
         <v>46125</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>46125</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28775,7 +28775,7 @@
         <v>46128</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>44574</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28931,7 +28931,7 @@
         <v>45509</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29004,7 +29004,7 @@
         <v>46128</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29082,7 +29082,7 @@
         <v>46132</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29160,7 +29160,7 @@
         <v>45743</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29233,7 +29233,7 @@
         <v>45296</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29306,7 +29306,7 @@
         <v>45163</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>46134</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29462,7 +29462,7 @@
         <v>46134</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29535,7 +29535,7 @@
         <v>45239</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29613,7 +29613,7 @@
         <v>45748</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29686,7 +29686,7 @@
         <v>46139</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29764,7 +29764,7 @@
         <v>45615</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29842,7 +29842,7 @@
         <v>45573</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29920,7 +29920,7 @@
         <v>45573</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29998,7 +29998,7 @@
         <v>45551</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30076,7 +30076,7 @@
         <v>44575</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30149,7 +30149,7 @@
         <v>46212</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30227,7 +30227,7 @@
         <v>45757</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30300,7 +30300,7 @@
         <v>45086</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30378,7 +30378,7 @@
         <v>44733</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30451,7 +30451,7 @@
         <v>44911</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30524,7 +30524,7 @@
         <v>45278</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30597,7 +30597,7 @@
         <v>46225</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>44495</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30748,7 +30748,7 @@
         <v>46273</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30826,7 +30826,7 @@
         <v>45268</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30899,7 +30899,7 @@
         <v>46279</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30977,7 +30977,7 @@
         <v>46279</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>44509</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31128,7 +31128,7 @@
         <v>46167</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>46279</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31284,7 +31284,7 @@
         <v>45358</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31357,7 +31357,7 @@
         <v>45239</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31435,7 +31435,7 @@
         <v>46281</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31513,7 +31513,7 @@
         <v>46281</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31591,7 +31591,7 @@
         <v>46281</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31669,7 +31669,7 @@
         <v>46281</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31747,7 +31747,7 @@
         <v>46281</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31820,7 +31820,7 @@
         <v>46240</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31893,7 +31893,7 @@
         <v>46240</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31966,7 +31966,7 @@
         <v>45757</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32039,7 +32039,7 @@
         <v>46281</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32117,7 +32117,7 @@
         <v>46282</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32190,7 +32190,7 @@
         <v>46239</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32268,7 +32268,7 @@
         <v>46281</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>45541</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32424,7 +32424,7 @@
         <v>46286</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32497,7 +32497,7 @@
         <v>46244</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32570,7 +32570,7 @@
         <v>46058</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32643,7 +32643,7 @@
         <v>46178</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32721,7 +32721,7 @@
         <v>45701</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32794,7 +32794,7 @@
         <v>45957</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32867,7 +32867,7 @@
         <v>45958</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32945,7 +32945,7 @@
         <v>45958</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33023,7 +33023,7 @@
         <v>46290</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33101,7 +33101,7 @@
         <v>44909</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>45086</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33252,7 +33252,7 @@
         <v>46174</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33330,7 +33330,7 @@
         <v>45194</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33403,7 +33403,7 @@
         <v>45173</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33481,7 +33481,7 @@
         <v>45055</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33559,7 +33559,7 @@
         <v>44529</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33632,7 +33632,7 @@
         <v>45113</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33710,7 +33710,7 @@
         <v>46296</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33788,7 +33788,7 @@
         <v>46072</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33861,7 +33861,7 @@
         <v>46072</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33934,7 +33934,7 @@
         <v>45111</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34012,7 +34012,7 @@
         <v>45278</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34085,7 +34085,7 @@
         <v>45590</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34158,7 +34158,7 @@
         <v>45187</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34236,7 +34236,7 @@
         <v>46301</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34309,7 +34309,7 @@
         <v>46300</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34382,7 +34382,7 @@
         <v>45337</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34455,7 +34455,7 @@
         <v>46255</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34533,7 +34533,7 @@
         <v>46255</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34611,7 +34611,7 @@
         <v>45603</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34684,7 +34684,7 @@
         <v>46255</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34762,7 +34762,7 @@
         <v>46212</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34840,7 +34840,7 @@
         <v>45462</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34918,7 +34918,7 @@
         <v>45799</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34991,7 +34991,7 @@
         <v>46262</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35064,7 +35064,7 @@
         <v>45429</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35137,7 +35137,7 @@
         <v>46266</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35215,7 +35215,7 @@
         <v>46266</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35293,7 +35293,7 @@
         <v>45569</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35366,7 +35366,7 @@
         <v>45701</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35439,7 +35439,7 @@
         <v>45818</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35517,7 +35517,7 @@
         <v>45818</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35595,7 +35595,7 @@
         <v>45827</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35668,7 +35668,7 @@
         <v>45840</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35746,7 +35746,7 @@
         <v>45840</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35824,7 +35824,7 @@
         <v>45848</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>45743</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35975,7 +35975,7 @@
         <v>45866</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36048,7 +36048,7 @@
         <v>45866</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36126,7 +36126,7 @@
         <v>45867</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36199,7 +36199,7 @@
         <v>45784</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36277,7 +36277,7 @@
         <v>44102</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36355,7 +36355,7 @@
         <v>45700</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>45700</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36511,7 +36511,7 @@
         <v>44550</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36589,7 +36589,7 @@
         <v>45317</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36667,7 +36667,7 @@
         <v>45316</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36745,7 +36745,7 @@
         <v>44671</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36823,7 +36823,7 @@
         <v>45720</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36901,7 +36901,7 @@
         <v>45706</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36979,7 +36979,7 @@
         <v>45906</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37057,7 +37057,7 @@
         <v>45989</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37135,7 +37135,7 @@
         <v>45995</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37213,7 +37213,7 @@
         <v>46070</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37291,7 +37291,7 @@
         <v>45700</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37369,7 +37369,7 @@
         <v>46142</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37447,7 +37447,7 @@
         <v>46125</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37525,7 +37525,7 @@
         <v>45971</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37598,7 +37598,7 @@
         <v>46085</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>

--- a/Översikt HEDEMORA.xlsx
+++ b/Översikt HEDEMORA.xlsx
@@ -601,7 +601,7 @@
         <v>45105</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>45996</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>44655</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>46197</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>45180</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>46033</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>45239</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>45628</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>45527</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>46033</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>44502</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>45527</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>45940</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>45616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>45919</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>46150</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>45527</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>46078</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>46020</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>46178</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>45961</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>45702</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>45301</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         <v>46251</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>45527</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>45887</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>45897</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>45469</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>46178</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>46033</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>46055</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>45702</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>46062</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>44588</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>46198</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>46239</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>46033</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>46198</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>44502</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>46048</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>46051</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>45933</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>46239</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>46051</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>44582</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>44579</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         <v>45664</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>44961</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>45565</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>44550</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>44523</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>45171</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>45527</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>46177</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>46176</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         <v>46178</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>46178</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>46185</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>44883</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>46000</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>46240</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>44945</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>46070</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>45821</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         <v>45825</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8306,7 +8306,7 @@
         <v>45670</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>46146</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
         <v>46157</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>45642</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>45001</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>44550</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>44585</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>45317</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>44880</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>44574</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         <v>44880</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>44864</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>45889</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         <v>46164</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>45743</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>45842</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>46177</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10202,7 +10202,7 @@
         <v>45933</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10312,7 +10312,7 @@
         <v>46204</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
         <v>46212</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
         <v>46213</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>46245</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>46062</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>45441</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         <v>45008</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>45818</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>45818</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
         <v>46296</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>46300</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         <v>46300</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>45743</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11727,7 +11727,7 @@
         <v>45743</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>45767</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>44918</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12052,7 +12052,7 @@
         <v>45275</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>46266</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
         <v>46105</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>45226</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         <v>45610</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12609,7 +12609,7 @@
         <v>45757</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         <v>44680</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
         <v>45763</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12924,7 +12924,7 @@
         <v>45615</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13034,7 +13034,7 @@
         <v>44550</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13144,7 +13144,7 @@
         <v>45319</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>45316</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>46069</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>44523</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13564,7 +13564,7 @@
         <v>44565</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>44783</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13710,7 +13710,7 @@
         <v>44846</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13788,7 +13788,7 @@
         <v>44802</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13861,7 +13861,7 @@
         <v>44698</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13934,7 +13934,7 @@
         <v>44529</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
         <v>44588</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>44817</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>44741</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14236,7 +14236,7 @@
         <v>44720</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>44502</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
         <v>44746</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
         <v>44859</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14538,7 +14538,7 @@
         <v>44495</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
         <v>44575</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
         <v>45626</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14762,7 +14762,7 @@
         <v>45534</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14840,7 +14840,7 @@
         <v>45743</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14913,7 +14913,7 @@
         <v>45889</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>45889</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15069,7 +15069,7 @@
         <v>45770</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>45770</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>45895</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>45172</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15371,7 +15371,7 @@
         <v>45113</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>44909</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15522,7 +15522,7 @@
         <v>45230</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>45906</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>46164</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15751,7 +15751,7 @@
         <v>46161</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>45190</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15902,7 +15902,7 @@
         <v>46163</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15975,7 +15975,7 @@
         <v>45694</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>46167</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>44733</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16199,7 +16199,7 @@
         <v>46169</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16277,7 +16277,7 @@
         <v>46169</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16355,7 +16355,7 @@
         <v>46062</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16428,7 +16428,7 @@
         <v>45933</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>45230</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>46030</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
         <v>46174</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16725,7 +16725,7 @@
         <v>46174</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16803,7 +16803,7 @@
         <v>45541</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16881,7 +16881,7 @@
         <v>46177</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>46177</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17037,7 +17037,7 @@
         <v>44817</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>45239</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
         <v>46099</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>46178</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>46114</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17422,7 +17422,7 @@
         <v>45943</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17495,7 +17495,7 @@
         <v>45919</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>46178</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>45920</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>45940</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17807,7 +17807,7 @@
         <v>46033</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17880,7 +17880,7 @@
         <v>46136</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17958,7 +17958,7 @@
         <v>45951</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18031,7 +18031,7 @@
         <v>46136</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
         <v>46136</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18187,7 +18187,7 @@
         <v>45951</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18260,7 +18260,7 @@
         <v>45953</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18338,7 +18338,7 @@
         <v>45952</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         <v>46183</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18489,7 +18489,7 @@
         <v>45583</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18562,7 +18562,7 @@
         <v>45610</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         <v>46185</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18718,7 +18718,7 @@
         <v>46148</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18796,7 +18796,7 @@
         <v>45963</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18869,7 +18869,7 @@
         <v>45070</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18942,7 +18942,7 @@
         <v>45792</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         <v>45784</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19098,7 +19098,7 @@
         <v>44783</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         <v>45840</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19249,7 +19249,7 @@
         <v>45968</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19322,7 +19322,7 @@
         <v>45933</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19395,7 +19395,7 @@
         <v>45889</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19473,7 +19473,7 @@
         <v>45840</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>45971</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19624,7 +19624,7 @@
         <v>46198</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>45558</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>45973</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>45975</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19926,7 +19926,7 @@
         <v>45230</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19999,7 +19999,7 @@
         <v>45880</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>45623</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20150,7 +20150,7 @@
         <v>45880</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20228,7 +20228,7 @@
         <v>45610</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20306,7 +20306,7 @@
         <v>45086</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>46212</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>45615</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>45743</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>46225</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>45278</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20764,7 +20764,7 @@
         <v>45187</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20842,7 +20842,7 @@
         <v>45337</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20915,7 +20915,7 @@
         <v>45111</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20993,7 +20993,7 @@
         <v>45905</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>46167</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21149,7 +21149,7 @@
         <v>46007</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
         <v>46279</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21300,7 +21300,7 @@
         <v>46279</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>45505</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21451,7 +21451,7 @@
         <v>45590</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21524,7 +21524,7 @@
         <v>46279</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21602,7 +21602,7 @@
         <v>45603</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         <v>46020</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21748,7 +21748,7 @@
         <v>46020</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21821,7 +21821,7 @@
         <v>46281</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
         <v>46282</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>45459</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22040,7 +22040,7 @@
         <v>45940</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22118,7 +22118,7 @@
         <v>46021</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22191,7 +22191,7 @@
         <v>46281</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22269,7 +22269,7 @@
         <v>46281</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22347,7 +22347,7 @@
         <v>46239</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22425,7 +22425,7 @@
         <v>46281</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22503,7 +22503,7 @@
         <v>46281</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>46030</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>46033</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22727,7 +22727,7 @@
         <v>46034</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22800,7 +22800,7 @@
         <v>46240</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>46035</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>46240</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23019,7 +23019,7 @@
         <v>46281</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23097,7 +23097,7 @@
         <v>46036</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23175,7 +23175,7 @@
         <v>46286</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>46037</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>46281</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23399,7 +23399,7 @@
         <v>45980</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23477,7 +23477,7 @@
         <v>46058</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23550,7 +23550,7 @@
         <v>46044</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23623,7 +23623,7 @@
         <v>45462</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23701,7 +23701,7 @@
         <v>46043</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23774,7 +23774,7 @@
         <v>46032</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23847,7 +23847,7 @@
         <v>46244</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23920,7 +23920,7 @@
         <v>46050</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23993,7 +23993,7 @@
         <v>45799</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24066,7 +24066,7 @@
         <v>45429</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24139,7 +24139,7 @@
         <v>46178</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>46051</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         <v>46051</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24363,7 +24363,7 @@
         <v>46051</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24436,7 +24436,7 @@
         <v>45701</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>45569</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>45252</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>45260</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24728,7 +24728,7 @@
         <v>46048</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24801,7 +24801,7 @@
         <v>45818</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24879,7 +24879,7 @@
         <v>46290</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24957,7 +24957,7 @@
         <v>45818</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25035,7 +25035,7 @@
         <v>46174</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25113,7 +25113,7 @@
         <v>46066</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25191,7 +25191,7 @@
         <v>45958</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25269,7 +25269,7 @@
         <v>45958</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25347,7 +25347,7 @@
         <v>45509</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         <v>45957</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25493,7 +25493,7 @@
         <v>45086</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25571,7 +25571,7 @@
         <v>46072</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25644,7 +25644,7 @@
         <v>46296</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25722,7 +25722,7 @@
         <v>45989</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25800,7 +25800,7 @@
         <v>45995</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25878,7 +25878,7 @@
         <v>45827</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>46072</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>46072</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26097,7 +26097,7 @@
         <v>46084</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>46255</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>46090</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>46300</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26394,7 +26394,7 @@
         <v>46094</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26467,7 +26467,7 @@
         <v>46255</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26545,7 +26545,7 @@
         <v>45840</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26623,7 +26623,7 @@
         <v>46099</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26696,7 +26696,7 @@
         <v>45840</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26774,7 +26774,7 @@
         <v>46098</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26852,7 +26852,7 @@
         <v>46098</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>46098</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27003,7 +27003,7 @@
         <v>46098</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27081,7 +27081,7 @@
         <v>46098</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27154,7 +27154,7 @@
         <v>46099</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27232,7 +27232,7 @@
         <v>44914</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27305,7 +27305,7 @@
         <v>45848</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27378,7 +27378,7 @@
         <v>46105</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27456,7 +27456,7 @@
         <v>46105</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>46255</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>46108</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>45743</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27763,7 +27763,7 @@
         <v>46111</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>46301</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>46111</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27982,7 +27982,7 @@
         <v>45866</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>45866</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>45867</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>46125</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28279,7 +28279,7 @@
         <v>46124</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28357,7 +28357,7 @@
         <v>46122</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28435,7 +28435,7 @@
         <v>46125</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28508,7 +28508,7 @@
         <v>46262</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>46212</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28659,7 +28659,7 @@
         <v>46128</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28737,7 +28737,7 @@
         <v>46128</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>45784</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28893,7 +28893,7 @@
         <v>44917</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28966,7 +28966,7 @@
         <v>46134</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29044,7 +29044,7 @@
         <v>46132</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29122,7 +29122,7 @@
         <v>46134</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>45538</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29268,7 +29268,7 @@
         <v>45541</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29346,7 +29346,7 @@
         <v>46136</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29424,7 +29424,7 @@
         <v>46266</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29502,7 +29502,7 @@
         <v>46266</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29580,7 +29580,7 @@
         <v>46083</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29653,7 +29653,7 @@
         <v>46056</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         <v>44750</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29804,7 +29804,7 @@
         <v>45895</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29877,7 +29877,7 @@
         <v>45484</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29955,7 +29955,7 @@
         <v>45055</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30033,7 +30033,7 @@
         <v>45810</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30106,7 +30106,7 @@
         <v>45209</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30179,7 +30179,7 @@
         <v>45551</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30257,7 +30257,7 @@
         <v>46069</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30330,7 +30330,7 @@
         <v>45022</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30408,7 +30408,7 @@
         <v>46034</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30481,7 +30481,7 @@
         <v>45541</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30559,7 +30559,7 @@
         <v>44956</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30637,7 +30637,7 @@
         <v>46273</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30715,7 +30715,7 @@
         <v>46139</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30793,7 +30793,7 @@
         <v>46315</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30866,7 +30866,7 @@
         <v>45573</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30944,7 +30944,7 @@
         <v>45573</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>46020</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31095,7 +31095,7 @@
         <v>45230</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31168,7 +31168,7 @@
         <v>45576</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31241,7 +31241,7 @@
         <v>46114</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31319,7 +31319,7 @@
         <v>45469</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31392,7 +31392,7 @@
         <v>45630</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31465,7 +31465,7 @@
         <v>45254</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31538,7 +31538,7 @@
         <v>46157</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31616,7 +31616,7 @@
         <v>44509</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31689,7 +31689,7 @@
         <v>45233</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>45061</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>45268</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31913,7 +31913,7 @@
         <v>44805</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31991,7 +31991,7 @@
         <v>45708</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32064,7 +32064,7 @@
         <v>45748</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32137,7 +32137,7 @@
         <v>45729</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32210,7 +32210,7 @@
         <v>45216</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32283,7 +32283,7 @@
         <v>45070</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32356,7 +32356,7 @@
         <v>45230</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32429,7 +32429,7 @@
         <v>45474</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>44529</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32580,7 +32580,7 @@
         <v>45757</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>45099</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32726,7 +32726,7 @@
         <v>44900</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32799,7 +32799,7 @@
         <v>45104</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32877,7 +32877,7 @@
         <v>45278</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32950,7 +32950,7 @@
         <v>45702</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33023,7 +33023,7 @@
         <v>45566</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33101,7 +33101,7 @@
         <v>45350</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>44501</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33247,7 +33247,7 @@
         <v>45358</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33320,7 +33320,7 @@
         <v>44546</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33393,7 +33393,7 @@
         <v>45239</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33471,7 +33471,7 @@
         <v>45218</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33544,7 +33544,7 @@
         <v>45287</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>44628</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33695,7 +33695,7 @@
         <v>45163</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33773,7 +33773,7 @@
         <v>45474</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33851,7 +33851,7 @@
         <v>45407</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33929,7 +33929,7 @@
         <v>45429</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34002,7 +34002,7 @@
         <v>45170</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34075,7 +34075,7 @@
         <v>45617</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34153,7 +34153,7 @@
         <v>44532</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34226,7 +34226,7 @@
         <v>45278</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34299,7 +34299,7 @@
         <v>45342</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34372,7 +34372,7 @@
         <v>45551</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34450,7 +34450,7 @@
         <v>44662</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34528,7 +34528,7 @@
         <v>45350</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34601,7 +34601,7 @@
         <v>45610</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34679,7 +34679,7 @@
         <v>45729</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>45701</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34825,7 +34825,7 @@
         <v>45175</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>45756</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34971,7 +34971,7 @@
         <v>45253</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35044,7 +35044,7 @@
         <v>45194</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35117,7 +35117,7 @@
         <v>44792</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35190,7 +35190,7 @@
         <v>45316</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35263,7 +35263,7 @@
         <v>45268</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35336,7 +35336,7 @@
         <v>45757</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>45267</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35482,7 +35482,7 @@
         <v>44495</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35555,7 +35555,7 @@
         <v>45268</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35628,7 +35628,7 @@
         <v>45615</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35706,7 +35706,7 @@
         <v>45296</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35779,7 +35779,7 @@
         <v>45173</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35857,7 +35857,7 @@
         <v>44574</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35935,7 +35935,7 @@
         <v>44575</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36008,7 +36008,7 @@
         <v>44911</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36081,7 +36081,7 @@
         <v>44757</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36159,7 +36159,7 @@
         <v>44102</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>44550</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36315,7 +36315,7 @@
         <v>44671</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36393,7 +36393,7 @@
         <v>45700</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36471,7 +36471,7 @@
         <v>45700</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36549,7 +36549,7 @@
         <v>45317</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36627,7 +36627,7 @@
         <v>45316</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         <v>45720</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36783,7 +36783,7 @@
         <v>45706</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36861,7 +36861,7 @@
         <v>45906</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36939,7 +36939,7 @@
         <v>45989</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37017,7 +37017,7 @@
         <v>45995</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>46070</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37173,7 +37173,7 @@
         <v>45700</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37251,7 +37251,7 @@
         <v>46142</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37329,7 +37329,7 @@
         <v>46125</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37407,7 +37407,7 @@
         <v>45971</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37480,7 +37480,7 @@
         <v>46085</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>

--- a/Översikt HEDEMORA.xlsx
+++ b/Översikt HEDEMORA.xlsx
@@ -601,7 +601,7 @@
         <v>45105</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>45996</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>44655</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>46197</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>45180</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>46033</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>45239</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>45628</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>45527</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>46033</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>44502</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>45527</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>45940</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>45616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>45919</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>46150</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>45527</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>46078</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>46020</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>46178</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>45961</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>45702</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>45301</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         <v>46251</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>45527</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>45887</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>45897</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>45469</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>46178</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>46033</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>46055</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>45702</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>46062</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>44588</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>46198</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>46239</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>46033</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>46198</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>44502</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>46048</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>46051</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>45933</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>46239</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>46051</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>44582</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>44579</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         <v>45664</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>44961</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>45565</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>44550</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>44523</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>45171</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>45527</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>46177</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>46176</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         <v>46178</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>46178</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>46185</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>44883</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>46000</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>46240</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>44945</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>46070</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>45821</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         <v>45825</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8306,7 +8306,7 @@
         <v>45670</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>46146</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
         <v>46157</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>45642</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>45001</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>44550</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>44585</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>45317</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>44880</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>44574</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         <v>44880</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>44864</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>45889</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         <v>46164</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>45743</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>45842</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>46177</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10202,7 +10202,7 @@
         <v>45933</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10312,7 +10312,7 @@
         <v>46204</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
         <v>46212</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
         <v>46213</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>46245</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>46062</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>45441</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         <v>45008</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>45818</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>45818</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
         <v>46296</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>46300</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         <v>46300</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>45743</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11727,7 +11727,7 @@
         <v>45743</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>45767</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>44918</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12052,7 +12052,7 @@
         <v>45275</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>46266</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
         <v>46105</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>45226</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         <v>45610</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12609,7 +12609,7 @@
         <v>45757</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         <v>44680</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
         <v>45763</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12924,7 +12924,7 @@
         <v>45615</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13034,7 +13034,7 @@
         <v>44550</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13144,7 +13144,7 @@
         <v>45319</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>45316</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>46069</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>44523</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13564,7 +13564,7 @@
         <v>44565</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>44783</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13710,7 +13710,7 @@
         <v>44846</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13788,7 +13788,7 @@
         <v>44802</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13861,7 +13861,7 @@
         <v>44698</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13934,7 +13934,7 @@
         <v>44529</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
         <v>44588</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>44817</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>44741</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14236,7 +14236,7 @@
         <v>44720</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>44502</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
         <v>44746</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
         <v>44859</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14538,7 +14538,7 @@
         <v>44495</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
         <v>44575</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
         <v>45626</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14762,7 +14762,7 @@
         <v>45534</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14840,7 +14840,7 @@
         <v>45743</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14913,7 +14913,7 @@
         <v>45889</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>45889</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15069,7 +15069,7 @@
         <v>45770</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>45770</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>45895</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>45172</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15371,7 +15371,7 @@
         <v>45113</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>44909</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15522,7 +15522,7 @@
         <v>45230</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>45906</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>46164</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15751,7 +15751,7 @@
         <v>46161</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>45190</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15902,7 +15902,7 @@
         <v>46163</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15975,7 +15975,7 @@
         <v>45694</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>46167</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>44733</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16199,7 +16199,7 @@
         <v>46169</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16277,7 +16277,7 @@
         <v>46169</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16355,7 +16355,7 @@
         <v>46062</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16428,7 +16428,7 @@
         <v>45933</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>45230</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>46030</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
         <v>46174</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16725,7 +16725,7 @@
         <v>46174</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16803,7 +16803,7 @@
         <v>45541</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16881,7 +16881,7 @@
         <v>46177</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>46177</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17037,7 +17037,7 @@
         <v>44817</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>45239</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
         <v>46099</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>46178</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>46114</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17422,7 +17422,7 @@
         <v>45943</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17495,7 +17495,7 @@
         <v>45919</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>46178</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>45920</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>45940</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17807,7 +17807,7 @@
         <v>46033</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17880,7 +17880,7 @@
         <v>46136</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17958,7 +17958,7 @@
         <v>45951</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18031,7 +18031,7 @@
         <v>46136</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
         <v>46136</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18187,7 +18187,7 @@
         <v>45951</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18260,7 +18260,7 @@
         <v>45953</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18338,7 +18338,7 @@
         <v>45952</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         <v>46183</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18489,7 +18489,7 @@
         <v>45583</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18562,7 +18562,7 @@
         <v>45610</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         <v>46185</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18718,7 +18718,7 @@
         <v>46148</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18796,7 +18796,7 @@
         <v>45963</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18869,7 +18869,7 @@
         <v>45070</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18942,7 +18942,7 @@
         <v>45792</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         <v>45784</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19098,7 +19098,7 @@
         <v>44783</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         <v>45840</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19249,7 +19249,7 @@
         <v>45968</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19322,7 +19322,7 @@
         <v>45933</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19395,7 +19395,7 @@
         <v>45889</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19473,7 +19473,7 @@
         <v>45840</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>45971</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19624,7 +19624,7 @@
         <v>46198</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>45558</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>45973</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>45975</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19926,7 +19926,7 @@
         <v>45230</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19999,7 +19999,7 @@
         <v>45880</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>45623</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20150,7 +20150,7 @@
         <v>45880</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20228,7 +20228,7 @@
         <v>45610</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20306,7 +20306,7 @@
         <v>45086</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>46212</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>45615</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>45743</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>46225</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>45278</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20764,7 +20764,7 @@
         <v>45187</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20842,7 +20842,7 @@
         <v>45337</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20915,7 +20915,7 @@
         <v>45111</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20993,7 +20993,7 @@
         <v>45905</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>46167</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21149,7 +21149,7 @@
         <v>46007</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
         <v>46279</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21300,7 +21300,7 @@
         <v>46279</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>45505</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21451,7 +21451,7 @@
         <v>45590</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21524,7 +21524,7 @@
         <v>46279</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21602,7 +21602,7 @@
         <v>45603</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         <v>46020</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21748,7 +21748,7 @@
         <v>46020</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21821,7 +21821,7 @@
         <v>46281</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
         <v>46282</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>45459</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22040,7 +22040,7 @@
         <v>45940</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22118,7 +22118,7 @@
         <v>46021</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22191,7 +22191,7 @@
         <v>46281</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22269,7 +22269,7 @@
         <v>46281</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22347,7 +22347,7 @@
         <v>46239</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22425,7 +22425,7 @@
         <v>46281</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22503,7 +22503,7 @@
         <v>46281</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>46030</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>46033</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22727,7 +22727,7 @@
         <v>46034</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22800,7 +22800,7 @@
         <v>46240</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>46035</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>46240</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23019,7 +23019,7 @@
         <v>46281</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23097,7 +23097,7 @@
         <v>46036</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23175,7 +23175,7 @@
         <v>46286</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>46037</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>46281</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23399,7 +23399,7 @@
         <v>45980</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23477,7 +23477,7 @@
         <v>46058</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23550,7 +23550,7 @@
         <v>46044</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23623,7 +23623,7 @@
         <v>45462</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23701,7 +23701,7 @@
         <v>46043</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23774,7 +23774,7 @@
         <v>46032</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23847,7 +23847,7 @@
         <v>46244</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23920,7 +23920,7 @@
         <v>46050</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23993,7 +23993,7 @@
         <v>45799</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24066,7 +24066,7 @@
         <v>45429</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24139,7 +24139,7 @@
         <v>46178</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>46051</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         <v>46051</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24363,7 +24363,7 @@
         <v>46051</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24436,7 +24436,7 @@
         <v>45701</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>45569</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>45252</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>45260</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24728,7 +24728,7 @@
         <v>46048</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24801,7 +24801,7 @@
         <v>45818</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24879,7 +24879,7 @@
         <v>46290</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24957,7 +24957,7 @@
         <v>45818</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25035,7 +25035,7 @@
         <v>46174</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25113,7 +25113,7 @@
         <v>46066</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25191,7 +25191,7 @@
         <v>45958</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25269,7 +25269,7 @@
         <v>45958</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25347,7 +25347,7 @@
         <v>45509</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         <v>45957</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25493,7 +25493,7 @@
         <v>45086</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25571,7 +25571,7 @@
         <v>46072</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25644,7 +25644,7 @@
         <v>46296</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25722,7 +25722,7 @@
         <v>45989</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25800,7 +25800,7 @@
         <v>45995</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25878,7 +25878,7 @@
         <v>45827</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>46072</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>46072</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26097,7 +26097,7 @@
         <v>46084</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>46255</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>46090</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>46300</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26394,7 +26394,7 @@
         <v>46094</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26467,7 +26467,7 @@
         <v>46255</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26545,7 +26545,7 @@
         <v>45840</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26623,7 +26623,7 @@
         <v>46099</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26696,7 +26696,7 @@
         <v>45840</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26774,7 +26774,7 @@
         <v>46098</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26852,7 +26852,7 @@
         <v>46098</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>46098</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27003,7 +27003,7 @@
         <v>46098</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27081,7 +27081,7 @@
         <v>46098</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27154,7 +27154,7 @@
         <v>46099</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27232,7 +27232,7 @@
         <v>44914</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27305,7 +27305,7 @@
         <v>45848</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27378,7 +27378,7 @@
         <v>46105</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27456,7 +27456,7 @@
         <v>46105</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>46255</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>46108</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>45743</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27763,7 +27763,7 @@
         <v>46111</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>46301</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>46111</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27982,7 +27982,7 @@
         <v>45866</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>45866</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>45867</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>46125</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28279,7 +28279,7 @@
         <v>46124</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28357,7 +28357,7 @@
         <v>46122</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28435,7 +28435,7 @@
         <v>46125</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28508,7 +28508,7 @@
         <v>46262</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>46212</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28659,7 +28659,7 @@
         <v>46128</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28737,7 +28737,7 @@
         <v>46128</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>45784</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28893,7 +28893,7 @@
         <v>44917</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28966,7 +28966,7 @@
         <v>46134</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29044,7 +29044,7 @@
         <v>46132</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29122,7 +29122,7 @@
         <v>46134</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>45538</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29268,7 +29268,7 @@
         <v>45541</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29346,7 +29346,7 @@
         <v>46136</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29424,7 +29424,7 @@
         <v>46266</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29502,7 +29502,7 @@
         <v>46266</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29580,7 +29580,7 @@
         <v>46083</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29653,7 +29653,7 @@
         <v>46056</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         <v>44750</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29804,7 +29804,7 @@
         <v>45895</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29877,7 +29877,7 @@
         <v>45484</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29955,7 +29955,7 @@
         <v>45055</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30033,7 +30033,7 @@
         <v>45810</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30106,7 +30106,7 @@
         <v>45209</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30179,7 +30179,7 @@
         <v>45551</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30257,7 +30257,7 @@
         <v>46069</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30330,7 +30330,7 @@
         <v>45022</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30408,7 +30408,7 @@
         <v>46034</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30481,7 +30481,7 @@
         <v>45541</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30559,7 +30559,7 @@
         <v>44956</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30637,7 +30637,7 @@
         <v>46273</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30715,7 +30715,7 @@
         <v>46139</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30793,7 +30793,7 @@
         <v>46315</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30866,7 +30866,7 @@
         <v>45573</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30944,7 +30944,7 @@
         <v>45573</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>46020</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31095,7 +31095,7 @@
         <v>45230</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31168,7 +31168,7 @@
         <v>45576</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31241,7 +31241,7 @@
         <v>46114</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31319,7 +31319,7 @@
         <v>45469</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31392,7 +31392,7 @@
         <v>45630</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31465,7 +31465,7 @@
         <v>45254</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31538,7 +31538,7 @@
         <v>46157</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31616,7 +31616,7 @@
         <v>44509</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31689,7 +31689,7 @@
         <v>45233</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>45061</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>45268</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31913,7 +31913,7 @@
         <v>44805</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31991,7 +31991,7 @@
         <v>45708</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32064,7 +32064,7 @@
         <v>45748</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32137,7 +32137,7 @@
         <v>45729</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32210,7 +32210,7 @@
         <v>45216</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32283,7 +32283,7 @@
         <v>45070</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32356,7 +32356,7 @@
         <v>45230</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32429,7 +32429,7 @@
         <v>45474</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>44529</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32580,7 +32580,7 @@
         <v>45757</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>45099</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32726,7 +32726,7 @@
         <v>44900</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32799,7 +32799,7 @@
         <v>45104</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32877,7 +32877,7 @@
         <v>45278</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32950,7 +32950,7 @@
         <v>45702</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33023,7 +33023,7 @@
         <v>45566</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33101,7 +33101,7 @@
         <v>45350</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>44501</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33247,7 +33247,7 @@
         <v>45358</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33320,7 +33320,7 @@
         <v>44546</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33393,7 +33393,7 @@
         <v>45239</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33471,7 +33471,7 @@
         <v>45218</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33544,7 +33544,7 @@
         <v>45287</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>44628</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33695,7 +33695,7 @@
         <v>45163</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33773,7 +33773,7 @@
         <v>45474</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33851,7 +33851,7 @@
         <v>45407</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33929,7 +33929,7 @@
         <v>45429</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34002,7 +34002,7 @@
         <v>45170</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34075,7 +34075,7 @@
         <v>45617</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34153,7 +34153,7 @@
         <v>44532</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34226,7 +34226,7 @@
         <v>45278</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34299,7 +34299,7 @@
         <v>45342</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34372,7 +34372,7 @@
         <v>45551</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34450,7 +34450,7 @@
         <v>44662</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34528,7 +34528,7 @@
         <v>45350</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34601,7 +34601,7 @@
         <v>45610</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34679,7 +34679,7 @@
         <v>45729</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>45701</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34825,7 +34825,7 @@
         <v>45175</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>45756</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34971,7 +34971,7 @@
         <v>45253</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35044,7 +35044,7 @@
         <v>45194</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35117,7 +35117,7 @@
         <v>44792</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35190,7 +35190,7 @@
         <v>45316</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35263,7 +35263,7 @@
         <v>45268</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35336,7 +35336,7 @@
         <v>45757</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>45267</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35482,7 +35482,7 @@
         <v>44495</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35555,7 +35555,7 @@
         <v>45268</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35628,7 +35628,7 @@
         <v>45615</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35706,7 +35706,7 @@
         <v>45296</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35779,7 +35779,7 @@
         <v>45173</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35857,7 +35857,7 @@
         <v>44574</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35935,7 +35935,7 @@
         <v>44575</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36008,7 +36008,7 @@
         <v>44911</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36081,7 +36081,7 @@
         <v>44757</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36159,7 +36159,7 @@
         <v>44102</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>44550</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36315,7 +36315,7 @@
         <v>44671</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36393,7 +36393,7 @@
         <v>45700</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36471,7 +36471,7 @@
         <v>45700</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36549,7 +36549,7 @@
         <v>45317</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36627,7 +36627,7 @@
         <v>45316</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         <v>45720</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36783,7 +36783,7 @@
         <v>45706</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36861,7 +36861,7 @@
         <v>45906</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36939,7 +36939,7 @@
         <v>45989</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37017,7 +37017,7 @@
         <v>45995</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>46070</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37173,7 +37173,7 @@
         <v>45700</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37251,7 +37251,7 @@
         <v>46142</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37329,7 +37329,7 @@
         <v>46125</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37407,7 +37407,7 @@
         <v>45971</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37480,7 +37480,7 @@
         <v>46085</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
